--- a/CodeVS/data/output/barge_cost_schedule_Export_test.xlsx
+++ b/CodeVS/data/output/barge_cost_schedule_Export_test.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="108">
   <si>
     <t>BargeId</t>
   </si>
@@ -70,6 +70,78 @@
     <t>AllTime</t>
   </si>
   <si>
+    <t>B_059</t>
+  </si>
+  <si>
+    <t>B_090</t>
+  </si>
+  <si>
+    <t>B_010</t>
+  </si>
+  <si>
+    <t>B_100</t>
+  </si>
+  <si>
+    <t>B_095</t>
+  </si>
+  <si>
+    <t>B_015</t>
+  </si>
+  <si>
+    <t>B_019</t>
+  </si>
+  <si>
+    <t>B_042</t>
+  </si>
+  <si>
+    <t>B_058</t>
+  </si>
+  <si>
+    <t>B_045</t>
+  </si>
+  <si>
+    <t>B_040</t>
+  </si>
+  <si>
+    <t>B_087</t>
+  </si>
+  <si>
+    <t>B_046</t>
+  </si>
+  <si>
+    <t>B_061</t>
+  </si>
+  <si>
+    <t>B_088</t>
+  </si>
+  <si>
+    <t>B_026</t>
+  </si>
+  <si>
+    <t>B_064</t>
+  </si>
+  <si>
+    <t>B_030</t>
+  </si>
+  <si>
+    <t>B_041</t>
+  </si>
+  <si>
+    <t>B_013</t>
+  </si>
+  <si>
+    <t>B_101</t>
+  </si>
+  <si>
+    <t>B_085</t>
+  </si>
+  <si>
+    <t>B_081</t>
+  </si>
+  <si>
+    <t>B_047</t>
+  </si>
+  <si>
     <t>B_032</t>
   </si>
   <si>
@@ -139,180 +211,108 @@
     <t>B_016</t>
   </si>
   <si>
-    <t>B_059</t>
-  </si>
-  <si>
-    <t>B_090</t>
-  </si>
-  <si>
-    <t>B_010</t>
-  </si>
-  <si>
-    <t>B_100</t>
-  </si>
-  <si>
-    <t>B_095</t>
-  </si>
-  <si>
-    <t>B_015</t>
-  </si>
-  <si>
-    <t>B_019</t>
-  </si>
-  <si>
-    <t>B_042</t>
-  </si>
-  <si>
-    <t>B_058</t>
-  </si>
-  <si>
-    <t>B_045</t>
-  </si>
-  <si>
-    <t>B_040</t>
-  </si>
-  <si>
-    <t>B_087</t>
-  </si>
-  <si>
-    <t>B_046</t>
-  </si>
-  <si>
-    <t>B_061</t>
-  </si>
-  <si>
-    <t>B_088</t>
-  </si>
-  <si>
-    <t>B_026</t>
-  </si>
-  <si>
-    <t>B_064</t>
-  </si>
-  <si>
-    <t>B_030</t>
-  </si>
-  <si>
-    <t>B_041</t>
-  </si>
-  <si>
-    <t>B_013</t>
+    <t>B_005</t>
+  </si>
+  <si>
+    <t>B_006</t>
+  </si>
+  <si>
+    <t>B_003</t>
+  </si>
+  <si>
+    <t>B_004</t>
   </si>
   <si>
     <t>B_102</t>
   </si>
   <si>
-    <t>B_085</t>
+    <t>B_063</t>
+  </si>
+  <si>
+    <t>B_071</t>
+  </si>
+  <si>
+    <t>B_022</t>
+  </si>
+  <si>
+    <t>B_094</t>
+  </si>
+  <si>
+    <t>B_020</t>
+  </si>
+  <si>
+    <t>B_068</t>
   </si>
   <si>
     <t>B_083</t>
   </si>
   <si>
-    <t>B_050</t>
-  </si>
-  <si>
-    <t>B_005</t>
-  </si>
-  <si>
-    <t>B_006</t>
-  </si>
-  <si>
-    <t>B_003</t>
-  </si>
-  <si>
-    <t>B_004</t>
-  </si>
-  <si>
-    <t>B_101</t>
-  </si>
-  <si>
-    <t>B_062</t>
-  </si>
-  <si>
-    <t>B_068</t>
-  </si>
-  <si>
     <t>B_027</t>
   </si>
   <si>
-    <t>B_097</t>
+    <t>B_099</t>
   </si>
   <si>
     <t>B_023</t>
   </si>
   <si>
-    <t>B_022</t>
-  </si>
-  <si>
-    <t>B_093</t>
-  </si>
-  <si>
-    <t>B_034</t>
-  </si>
-  <si>
     <t>B_028</t>
   </si>
   <si>
-    <t>B_081</t>
-  </si>
-  <si>
-    <t>B_020</t>
+    <t>RiverTB_09</t>
+  </si>
+  <si>
+    <t>SeaTB_12</t>
+  </si>
+  <si>
+    <t>RiverTB_01</t>
   </si>
   <si>
     <t>RiverTB_02</t>
   </si>
   <si>
+    <t>SeaTB_11</t>
+  </si>
+  <si>
+    <t>RiverTB_12</t>
+  </si>
+  <si>
+    <t>RiverTB_10</t>
+  </si>
+  <si>
+    <t>SeaTB_06</t>
+  </si>
+  <si>
+    <t>SeaTB_09</t>
+  </si>
+  <si>
+    <t>RiverTB_06</t>
+  </si>
+  <si>
+    <t>RiverTB_13</t>
+  </si>
+  <si>
+    <t>SeaTB_02</t>
+  </si>
+  <si>
+    <t>SeaTB_08</t>
+  </si>
+  <si>
     <t>SeaTB_07</t>
   </si>
   <si>
-    <t>RiverTB_13</t>
-  </si>
-  <si>
     <t>SeaTB_04</t>
   </si>
   <si>
     <t>RiverTB_11</t>
   </si>
   <si>
-    <t>SeaTB_08</t>
-  </si>
-  <si>
-    <t>RiverTB_06</t>
-  </si>
-  <si>
     <t>SeaTB_03</t>
   </si>
   <si>
     <t>RiverTB_08</t>
   </si>
   <si>
-    <t>SeaTB_02</t>
-  </si>
-  <si>
-    <t>RiverTB_12</t>
-  </si>
-  <si>
-    <t>RiverTB_01</t>
-  </si>
-  <si>
-    <t>RiverTB_09</t>
-  </si>
-  <si>
-    <t>SeaTB_12</t>
-  </si>
-  <si>
-    <t>SeaTB_11</t>
-  </si>
-  <si>
-    <t>RiverTB_10</t>
-  </si>
-  <si>
-    <t>SeaTB_06</t>
-  </si>
-  <si>
-    <t>SeaTB_09</t>
-  </si>
-  <si>
     <t>Order_50</t>
   </si>
   <si>
@@ -331,13 +331,10 @@
     <t>ST_045</t>
   </si>
   <si>
-    <t>ST_050</t>
+    <t>ST_049</t>
   </si>
   <si>
     <t>Collecting Barge - B_015 - (ST_001 to ST_001)</t>
-  </si>
-  <si>
-    <t>ST_049</t>
   </si>
   <si>
     <t>ST_013</t>
@@ -702,7 +699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R116"/>
+  <dimension ref="A1:R115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -781,16 +778,16 @@
         <v>0.3</v>
       </c>
       <c r="G2">
-        <v>2900</v>
+        <v>2250</v>
       </c>
       <c r="H2" s="2">
-        <v>45984.95833333334</v>
+        <v>45984.94791666666</v>
       </c>
       <c r="I2" s="2">
-        <v>45985</v>
+        <v>45985.01041666666</v>
       </c>
       <c r="J2" s="2">
-        <v>45986.11822543956</v>
+        <v>45986.18867476596</v>
       </c>
       <c r="K2" t="s">
         <v>102</v>
@@ -799,7 +796,7 @@
         <v>102</v>
       </c>
       <c r="N2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -811,7 +808,7 @@
         <v>2</v>
       </c>
       <c r="R2">
-        <v>27.83741054944445</v>
+        <v>29.77819438305556</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -825,22 +822,22 @@
         <v>99</v>
       </c>
       <c r="D3">
-        <v>11.35842716732944</v>
+        <v>11.71486316630421</v>
       </c>
       <c r="E3">
         <v>62.21893992770459</v>
       </c>
       <c r="F3">
-        <v>738.2977658764135</v>
+        <v>761.4661058097738</v>
       </c>
       <c r="G3">
-        <v>2900</v>
+        <v>2250</v>
       </c>
       <c r="H3" s="2">
         <v>45984.375</v>
       </c>
       <c r="J3" s="2">
-        <v>45985.02187890975</v>
+        <v>45985.03673040971</v>
       </c>
       <c r="K3" t="s">
         <v>103</v>
@@ -864,7 +861,7 @@
         <v>2</v>
       </c>
       <c r="R3">
-        <v>15.52509383388889</v>
+        <v>15.88152983305556</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -872,7 +869,7 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
         <v>99</v>
@@ -887,19 +884,19 @@
         <v>0.3</v>
       </c>
       <c r="G4">
-        <v>1800</v>
+        <v>3150</v>
       </c>
       <c r="H4" s="2">
-        <v>45984.95833333334</v>
+        <v>45983.86458333334</v>
       </c>
       <c r="I4" s="2">
-        <v>45985</v>
+        <v>45985.01041666666</v>
       </c>
       <c r="J4" s="2">
-        <v>45986.11822543956</v>
+        <v>45986.13427084097</v>
       </c>
       <c r="K4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M4" t="s">
         <v>102</v>
@@ -911,13 +908,13 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>11.08333333333333</v>
       </c>
       <c r="Q4">
         <v>2</v>
       </c>
       <c r="R4">
-        <v>27.83741054944445</v>
+        <v>54.47250018333333</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -931,22 +928,22 @@
         <v>99</v>
       </c>
       <c r="D5">
-        <v>11.35842716732944</v>
+        <v>11.71486316630421</v>
       </c>
       <c r="E5">
         <v>62.21893992770459</v>
       </c>
       <c r="F5">
-        <v>738.2977658764135</v>
+        <v>761.4661058097738</v>
       </c>
       <c r="G5">
-        <v>1800</v>
+        <v>3150</v>
       </c>
       <c r="H5" s="2">
         <v>45984.375</v>
       </c>
       <c r="J5" s="2">
-        <v>45985.02187890975</v>
+        <v>45985.03673040971</v>
       </c>
       <c r="K5" t="s">
         <v>103</v>
@@ -970,7 +967,7 @@
         <v>2</v>
       </c>
       <c r="R5">
-        <v>15.52509383388889</v>
+        <v>15.88152983305556</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -978,7 +975,7 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
         <v>99</v>
@@ -993,19 +990,19 @@
         <v>0.3</v>
       </c>
       <c r="G6">
-        <v>2250</v>
+        <v>1800</v>
       </c>
       <c r="H6" s="2">
-        <v>45984.95833333334</v>
+        <v>45983.86458333334</v>
       </c>
       <c r="I6" s="2">
-        <v>45985</v>
+        <v>45985.01041666666</v>
       </c>
       <c r="J6" s="2">
-        <v>45986.11822543956</v>
+        <v>45986.13427084097</v>
       </c>
       <c r="K6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M6" t="s">
         <v>102</v>
@@ -1017,13 +1014,13 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>11.08333333333333</v>
       </c>
       <c r="Q6">
         <v>2</v>
       </c>
       <c r="R6">
-        <v>27.83741054944445</v>
+        <v>54.47250018333333</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1037,22 +1034,22 @@
         <v>99</v>
       </c>
       <c r="D7">
-        <v>11.35842716732944</v>
+        <v>11.71486316630421</v>
       </c>
       <c r="E7">
         <v>62.21893992770459</v>
       </c>
       <c r="F7">
-        <v>738.2977658764135</v>
+        <v>761.4661058097738</v>
       </c>
       <c r="G7">
-        <v>2250</v>
+        <v>1800</v>
       </c>
       <c r="H7" s="2">
         <v>45984.375</v>
       </c>
       <c r="J7" s="2">
-        <v>45985.02187890975</v>
+        <v>45985.03673040971</v>
       </c>
       <c r="K7" t="s">
         <v>103</v>
@@ -1076,7 +1073,7 @@
         <v>2</v>
       </c>
       <c r="R7">
-        <v>15.52509383388889</v>
+        <v>15.88152983305556</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1099,37 +1096,37 @@
         <v>0.3</v>
       </c>
       <c r="G8">
-        <v>2250</v>
+        <v>2750</v>
       </c>
       <c r="H8" s="2">
-        <v>45984.9375</v>
+        <v>45983.86458333334</v>
       </c>
       <c r="I8" s="2">
-        <v>45985</v>
+        <v>45985.01041666666</v>
       </c>
       <c r="J8" s="2">
-        <v>45986.27906395431</v>
+        <v>45986.13427084097</v>
       </c>
       <c r="K8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M8" t="s">
         <v>102</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>11.08333333333333</v>
       </c>
       <c r="Q8">
         <v>2</v>
       </c>
       <c r="R8">
-        <v>32.19753490333333</v>
+        <v>54.47250018333333</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1143,22 +1140,22 @@
         <v>99</v>
       </c>
       <c r="D9">
-        <v>11.35842716732944</v>
+        <v>11.71486316630421</v>
       </c>
       <c r="E9">
         <v>62.21893992770459</v>
       </c>
       <c r="F9">
-        <v>738.2977658764135</v>
+        <v>761.4661058097738</v>
       </c>
       <c r="G9">
-        <v>2250</v>
+        <v>2750</v>
       </c>
       <c r="H9" s="2">
         <v>45984.375</v>
       </c>
       <c r="J9" s="2">
-        <v>45985.02187890975</v>
+        <v>45985.03673040971</v>
       </c>
       <c r="K9" t="s">
         <v>103</v>
@@ -1182,7 +1179,7 @@
         <v>2</v>
       </c>
       <c r="R9">
-        <v>15.52509383388889</v>
+        <v>15.88152983305556</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1190,7 +1187,7 @@
         <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
         <v>99</v>
@@ -1208,34 +1205,34 @@
         <v>3150</v>
       </c>
       <c r="H10" s="2">
-        <v>45984.9375</v>
+        <v>45986.11458333334</v>
       </c>
       <c r="I10" s="2">
-        <v>45985</v>
+        <v>45986.61458333334</v>
       </c>
       <c r="J10" s="2">
-        <v>45986.27906395431</v>
+        <v>45987.50375139587</v>
       </c>
       <c r="K10" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="M10" t="s">
         <v>102</v>
       </c>
       <c r="N10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R10">
-        <v>32.19753490333333</v>
+        <v>33.34003350083334</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1249,13 +1246,13 @@
         <v>99</v>
       </c>
       <c r="D11">
-        <v>11.35842716732944</v>
+        <v>11.71486316630421</v>
       </c>
       <c r="E11">
         <v>62.21893992770459</v>
       </c>
       <c r="F11">
-        <v>738.2977658764135</v>
+        <v>761.4661058097738</v>
       </c>
       <c r="G11">
         <v>3150</v>
@@ -1264,7 +1261,7 @@
         <v>45984.375</v>
       </c>
       <c r="J11" s="2">
-        <v>45985.02187890975</v>
+        <v>45985.03673040971</v>
       </c>
       <c r="K11" t="s">
         <v>103</v>
@@ -1288,7 +1285,7 @@
         <v>2</v>
       </c>
       <c r="R11">
-        <v>15.52509383388889</v>
+        <v>15.88152983305556</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1296,40 +1293,40 @@
         <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
         <v>99</v>
       </c>
       <c r="D12">
-        <v>0.01</v>
+        <v>11.11052498709011</v>
       </c>
       <c r="E12">
-        <v>145</v>
+        <v>62.21893992770459</v>
       </c>
       <c r="F12">
-        <v>0.3</v>
+        <v>722.1841241608569</v>
       </c>
       <c r="G12">
-        <v>3100</v>
+        <v>2200</v>
       </c>
       <c r="H12" s="2">
-        <v>45984.9375</v>
-      </c>
-      <c r="I12" s="2">
-        <v>45985</v>
+        <v>45984.20833333334</v>
       </c>
       <c r="J12" s="2">
-        <v>45986.27906395431</v>
+        <v>45985.01154965225</v>
       </c>
       <c r="K12" t="s">
-        <v>102</v>
+        <v>106</v>
+      </c>
+      <c r="L12" t="s">
+        <v>103</v>
       </c>
       <c r="M12" t="s">
         <v>102</v>
       </c>
       <c r="N12">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -1341,7 +1338,7 @@
         <v>2</v>
       </c>
       <c r="R12">
-        <v>32.19753490333333</v>
+        <v>19.27719165388889</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1349,35 +1346,35 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
         <v>99</v>
       </c>
       <c r="D13">
-        <v>10.79467394230661</v>
+        <v>0.01</v>
       </c>
       <c r="E13">
-        <v>62.21893992770459</v>
+        <v>144</v>
       </c>
       <c r="F13">
-        <v>323.8402182691982</v>
+        <v>0.3</v>
       </c>
       <c r="G13">
-        <v>3100</v>
+        <v>2200</v>
       </c>
       <c r="H13" s="2">
-        <v>45983.95833333334</v>
+        <v>45984.92708333334</v>
+      </c>
+      <c r="I13" s="2">
+        <v>45984.98958333334</v>
       </c>
       <c r="J13" s="2">
-        <v>45984.93241696982</v>
+        <v>45986.09673218481</v>
       </c>
       <c r="K13" t="s">
         <v>102</v>
       </c>
-      <c r="L13" t="s">
-        <v>103</v>
-      </c>
       <c r="M13" t="s">
         <v>102</v>
       </c>
@@ -1394,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="R13">
-        <v>23.37800727555555</v>
+        <v>28.07157243555556</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1402,40 +1399,40 @@
         <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
         <v>99</v>
       </c>
       <c r="D14">
-        <v>0.01</v>
+        <v>11.11052498709011</v>
       </c>
       <c r="E14">
-        <v>145</v>
+        <v>62.21893992770459</v>
       </c>
       <c r="F14">
-        <v>0.3</v>
+        <v>722.1841241608569</v>
       </c>
       <c r="G14">
-        <v>3150</v>
+        <v>2100</v>
       </c>
       <c r="H14" s="2">
-        <v>45984.9375</v>
-      </c>
-      <c r="I14" s="2">
-        <v>45985</v>
+        <v>45984.20833333334</v>
       </c>
       <c r="J14" s="2">
-        <v>45986.27906395431</v>
+        <v>45985.01154965225</v>
       </c>
       <c r="K14" t="s">
-        <v>102</v>
+        <v>106</v>
+      </c>
+      <c r="L14" t="s">
+        <v>103</v>
       </c>
       <c r="M14" t="s">
         <v>102</v>
       </c>
       <c r="N14">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1447,7 +1444,7 @@
         <v>2</v>
       </c>
       <c r="R14">
-        <v>32.19753490333333</v>
+        <v>19.27719165388889</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1455,35 +1452,35 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
         <v>99</v>
       </c>
       <c r="D15">
-        <v>10.79467394230661</v>
+        <v>0.01</v>
       </c>
       <c r="E15">
-        <v>62.21893992770459</v>
+        <v>144</v>
       </c>
       <c r="F15">
-        <v>323.8402182691982</v>
+        <v>0.3</v>
       </c>
       <c r="G15">
-        <v>3150</v>
+        <v>2100</v>
       </c>
       <c r="H15" s="2">
-        <v>45983.95833333334</v>
+        <v>45984.92708333334</v>
+      </c>
+      <c r="I15" s="2">
+        <v>45984.98958333334</v>
       </c>
       <c r="J15" s="2">
-        <v>45984.93241696982</v>
+        <v>45986.09673218481</v>
       </c>
       <c r="K15" t="s">
         <v>102</v>
       </c>
-      <c r="L15" t="s">
-        <v>103</v>
-      </c>
       <c r="M15" t="s">
         <v>102</v>
       </c>
@@ -1500,7 +1497,7 @@
         <v>2</v>
       </c>
       <c r="R15">
-        <v>23.37800727555555</v>
+        <v>28.07157243555556</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1508,7 +1505,7 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
         <v>99</v>
@@ -1523,16 +1520,16 @@
         <v>0.3</v>
       </c>
       <c r="G16">
-        <v>2250</v>
+        <v>3000</v>
       </c>
       <c r="H16" s="2">
-        <v>45984.84375</v>
+        <v>45984.92708333334</v>
       </c>
       <c r="I16" s="2">
-        <v>45984.90625</v>
+        <v>45984.98958333334</v>
       </c>
       <c r="J16" s="2">
-        <v>45986.20849215214</v>
+        <v>45986.21342477692</v>
       </c>
       <c r="K16" t="s">
         <v>102</v>
@@ -1553,7 +1550,7 @@
         <v>2</v>
       </c>
       <c r="R16">
-        <v>32.75381165138889</v>
+        <v>30.87219464611111</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -1561,31 +1558,31 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
         <v>99</v>
       </c>
       <c r="D17">
-        <v>10.79467394230661</v>
+        <v>11.11052498709011</v>
       </c>
       <c r="E17">
         <v>62.21893992770459</v>
       </c>
       <c r="F17">
-        <v>323.8402182691982</v>
+        <v>722.1841241608569</v>
       </c>
       <c r="G17">
-        <v>2250</v>
+        <v>3000</v>
       </c>
       <c r="H17" s="2">
-        <v>45983.95833333334</v>
+        <v>45984.20833333334</v>
       </c>
       <c r="J17" s="2">
-        <v>45984.93241696982</v>
+        <v>45985.01154965225</v>
       </c>
       <c r="K17" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="L17" t="s">
         <v>103</v>
@@ -1594,7 +1591,7 @@
         <v>102</v>
       </c>
       <c r="N17">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -1606,7 +1603,7 @@
         <v>2</v>
       </c>
       <c r="R17">
-        <v>23.37800727555555</v>
+        <v>19.27719165388889</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -1614,7 +1611,7 @@
         <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
         <v>99</v>
@@ -1629,16 +1626,16 @@
         <v>0.3</v>
       </c>
       <c r="G18">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="H18" s="2">
-        <v>45984.84375</v>
+        <v>45984.92708333334</v>
       </c>
       <c r="I18" s="2">
-        <v>45984.90625</v>
+        <v>45984.98958333334</v>
       </c>
       <c r="J18" s="2">
-        <v>45986.20849215214</v>
+        <v>45986.21342477692</v>
       </c>
       <c r="K18" t="s">
         <v>102</v>
@@ -1659,7 +1656,7 @@
         <v>2</v>
       </c>
       <c r="R18">
-        <v>32.75381165138889</v>
+        <v>30.87219464611111</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -1667,31 +1664,31 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
         <v>99</v>
       </c>
       <c r="D19">
-        <v>10.79467394230661</v>
+        <v>11.11052498709011</v>
       </c>
       <c r="E19">
         <v>62.21893992770459</v>
       </c>
       <c r="F19">
-        <v>323.8402182691982</v>
+        <v>722.1841241608569</v>
       </c>
       <c r="G19">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="H19" s="2">
-        <v>45983.95833333334</v>
+        <v>45984.20833333334</v>
       </c>
       <c r="J19" s="2">
-        <v>45984.93241696982</v>
+        <v>45985.01154965225</v>
       </c>
       <c r="K19" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="L19" t="s">
         <v>103</v>
@@ -1700,7 +1697,7 @@
         <v>102</v>
       </c>
       <c r="N19">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -1712,7 +1709,7 @@
         <v>2</v>
       </c>
       <c r="R19">
-        <v>23.37800727555555</v>
+        <v>19.27719165388889</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -1720,7 +1717,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
         <v>99</v>
@@ -1735,16 +1732,16 @@
         <v>0.3</v>
       </c>
       <c r="G20">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="H20" s="2">
-        <v>45984.84375</v>
+        <v>45984.92708333334</v>
       </c>
       <c r="I20" s="2">
-        <v>45984.90625</v>
+        <v>45984.98958333334</v>
       </c>
       <c r="J20" s="2">
-        <v>45986.20849215214</v>
+        <v>45986.21342477692</v>
       </c>
       <c r="K20" t="s">
         <v>102</v>
@@ -1765,7 +1762,7 @@
         <v>2</v>
       </c>
       <c r="R20">
-        <v>32.75381165138889</v>
+        <v>30.87219464611111</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -1773,31 +1770,31 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
         <v>99</v>
       </c>
       <c r="D21">
-        <v>9.967111735991512</v>
+        <v>11.11052498709011</v>
       </c>
       <c r="E21">
         <v>62.21893992770459</v>
       </c>
       <c r="F21">
-        <v>647.8622628394482</v>
+        <v>722.1841241608569</v>
       </c>
       <c r="G21">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="H21" s="2">
-        <v>45984.375</v>
+        <v>45984.20833333334</v>
       </c>
       <c r="J21" s="2">
-        <v>45984.92918521123</v>
+        <v>45985.01154965225</v>
       </c>
       <c r="K21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L21" t="s">
         <v>103</v>
@@ -1806,7 +1803,7 @@
         <v>102</v>
       </c>
       <c r="N21">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -1818,7 +1815,7 @@
         <v>2</v>
       </c>
       <c r="R21">
-        <v>13.30044506944444</v>
+        <v>19.27719165388889</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -1826,7 +1823,7 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
         <v>99</v>
@@ -1841,16 +1838,16 @@
         <v>0.3</v>
       </c>
       <c r="G22">
-        <v>4750</v>
+        <v>2250</v>
       </c>
       <c r="H22" s="2">
-        <v>45984.84375</v>
+        <v>45984.92708333334</v>
       </c>
       <c r="I22" s="2">
-        <v>45984.90625</v>
+        <v>45984.98958333334</v>
       </c>
       <c r="J22" s="2">
-        <v>45986.20849215214</v>
+        <v>45986.21342477692</v>
       </c>
       <c r="K22" t="s">
         <v>102</v>
@@ -1871,7 +1868,7 @@
         <v>2</v>
       </c>
       <c r="R22">
-        <v>32.75381165138889</v>
+        <v>30.87219464611111</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -1879,37 +1876,34 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
         <v>99</v>
       </c>
       <c r="D23">
-        <v>9.967111735991512</v>
+        <v>10.70374352527781</v>
       </c>
       <c r="E23">
         <v>62.21893992770459</v>
       </c>
       <c r="F23">
-        <v>647.8622628394482</v>
+        <v>695.7433291430575</v>
       </c>
       <c r="G23">
-        <v>4750</v>
+        <v>2250</v>
       </c>
       <c r="H23" s="2">
-        <v>45984.375</v>
+        <v>45982.71908524904</v>
       </c>
       <c r="J23" s="2">
-        <v>45984.92918521123</v>
+        <v>45983.52271345148</v>
       </c>
       <c r="K23" t="s">
-        <v>103</v>
-      </c>
-      <c r="L23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M23" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="N23">
         <v>2</v>
@@ -1924,7 +1918,7 @@
         <v>2</v>
       </c>
       <c r="R23">
-        <v>13.30044506944444</v>
+        <v>19.28707685861111</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -1932,7 +1926,7 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s">
         <v>99</v>
@@ -1947,16 +1941,16 @@
         <v>0.3</v>
       </c>
       <c r="G24">
-        <v>2500</v>
+        <v>3300</v>
       </c>
       <c r="H24" s="2">
-        <v>45984.86458333334</v>
+        <v>45984.94791666666</v>
       </c>
       <c r="I24" s="2">
-        <v>45984.90625</v>
+        <v>45985.01041666666</v>
       </c>
       <c r="J24" s="2">
-        <v>45985.99060296014</v>
+        <v>45986.18867476596</v>
       </c>
       <c r="K24" t="s">
         <v>102</v>
@@ -1965,7 +1959,7 @@
         <v>102</v>
       </c>
       <c r="N24">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -1977,7 +1971,7 @@
         <v>2</v>
       </c>
       <c r="R24">
-        <v>27.02447104333333</v>
+        <v>29.77819438305556</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -1985,37 +1979,34 @@
         <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
         <v>99</v>
       </c>
       <c r="D25">
-        <v>9.967111735991512</v>
+        <v>10.70374352527781</v>
       </c>
       <c r="E25">
         <v>62.21893992770459</v>
       </c>
       <c r="F25">
-        <v>647.8622628394482</v>
+        <v>695.7433291430575</v>
       </c>
       <c r="G25">
-        <v>2500</v>
+        <v>3300</v>
       </c>
       <c r="H25" s="2">
-        <v>45984.375</v>
+        <v>45982.71908524904</v>
       </c>
       <c r="J25" s="2">
-        <v>45984.92918521123</v>
+        <v>45983.52271345148</v>
       </c>
       <c r="K25" t="s">
-        <v>103</v>
-      </c>
-      <c r="L25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M25" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="N25">
         <v>2</v>
@@ -2030,7 +2021,7 @@
         <v>2</v>
       </c>
       <c r="R25">
-        <v>13.30044506944444</v>
+        <v>19.28707685861111</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2038,7 +2029,7 @@
         <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s">
         <v>99</v>
@@ -2056,13 +2047,13 @@
         <v>2250</v>
       </c>
       <c r="H26" s="2">
-        <v>45984.86458333334</v>
+        <v>45984.94791666666</v>
       </c>
       <c r="I26" s="2">
-        <v>45984.90625</v>
+        <v>45985.01041666666</v>
       </c>
       <c r="J26" s="2">
-        <v>45985.99060296014</v>
+        <v>45986.18867476596</v>
       </c>
       <c r="K26" t="s">
         <v>102</v>
@@ -2071,7 +2062,7 @@
         <v>102</v>
       </c>
       <c r="N26">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -2083,7 +2074,7 @@
         <v>2</v>
       </c>
       <c r="R26">
-        <v>27.02447104333333</v>
+        <v>29.77819438305556</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -2091,37 +2082,34 @@
         <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
         <v>99</v>
       </c>
       <c r="D27">
-        <v>9.967111735991512</v>
+        <v>10.70374352527781</v>
       </c>
       <c r="E27">
         <v>62.21893992770459</v>
       </c>
       <c r="F27">
-        <v>647.8622628394482</v>
+        <v>695.7433291430575</v>
       </c>
       <c r="G27">
         <v>2250</v>
       </c>
       <c r="H27" s="2">
-        <v>45984.375</v>
+        <v>45982.71908524904</v>
       </c>
       <c r="J27" s="2">
-        <v>45984.92918521123</v>
+        <v>45983.52271345148</v>
       </c>
       <c r="K27" t="s">
-        <v>103</v>
-      </c>
-      <c r="L27" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M27" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="N27">
         <v>2</v>
@@ -2136,7 +2124,7 @@
         <v>2</v>
       </c>
       <c r="R27">
-        <v>13.30044506944444</v>
+        <v>19.28707685861111</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -2144,7 +2132,7 @@
         <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C28" t="s">
         <v>99</v>
@@ -2162,13 +2150,13 @@
         <v>2250</v>
       </c>
       <c r="H28" s="2">
-        <v>45984.86458333334</v>
+        <v>45984.94791666666</v>
       </c>
       <c r="I28" s="2">
-        <v>45984.90625</v>
+        <v>45985.01041666666</v>
       </c>
       <c r="J28" s="2">
-        <v>45985.99060296014</v>
+        <v>45986.18867476596</v>
       </c>
       <c r="K28" t="s">
         <v>102</v>
@@ -2177,7 +2165,7 @@
         <v>102</v>
       </c>
       <c r="N28">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -2189,7 +2177,7 @@
         <v>2</v>
       </c>
       <c r="R28">
-        <v>27.02447104333333</v>
+        <v>29.77819438305556</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -2203,34 +2191,31 @@
         <v>99</v>
       </c>
       <c r="D29">
-        <v>9.110310455088765</v>
+        <v>10.70374352527781</v>
       </c>
       <c r="E29">
         <v>62.21893992770459</v>
       </c>
       <c r="F29">
-        <v>592.1701795807697</v>
+        <v>695.7433291430575</v>
       </c>
       <c r="G29">
         <v>2250</v>
       </c>
       <c r="H29" s="2">
-        <v>45984.35416666666</v>
+        <v>45982.71908524904</v>
       </c>
       <c r="J29" s="2">
-        <v>45984.83792960229</v>
+        <v>45983.52271345148</v>
       </c>
       <c r="K29" t="s">
-        <v>103</v>
-      </c>
-      <c r="L29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M29" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="N29">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -2242,7 +2227,7 @@
         <v>2</v>
       </c>
       <c r="R29">
-        <v>11.610310455</v>
+        <v>19.28707685861111</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -2250,7 +2235,7 @@
         <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C30" t="s">
         <v>99</v>
@@ -2265,37 +2250,37 @@
         <v>0.3</v>
       </c>
       <c r="G30">
-        <v>2500</v>
+        <v>3150</v>
       </c>
       <c r="H30" s="2">
-        <v>45984.78125</v>
+        <v>45986.11458333334</v>
       </c>
       <c r="I30" s="2">
-        <v>45984.82291666666</v>
+        <v>45986.61458333334</v>
       </c>
       <c r="J30" s="2">
-        <v>45986.02323661984</v>
+        <v>45987.50375139587</v>
       </c>
       <c r="K30" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="M30" t="s">
         <v>102</v>
       </c>
       <c r="N30">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R30">
-        <v>29.80767887611111</v>
+        <v>33.34003350083334</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -2303,40 +2288,37 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
         <v>99</v>
       </c>
       <c r="D31">
-        <v>9.110310455088765</v>
+        <v>9.702185552813946</v>
       </c>
       <c r="E31">
         <v>62.21893992770459</v>
       </c>
       <c r="F31">
-        <v>592.1701795807697</v>
+        <v>630.6420609329065</v>
       </c>
       <c r="G31">
-        <v>2500</v>
+        <v>3150</v>
       </c>
       <c r="H31" s="2">
-        <v>45984.35416666666</v>
+        <v>45982.71908524904</v>
       </c>
       <c r="J31" s="2">
-        <v>45984.83792960229</v>
+        <v>45983.4809818693</v>
       </c>
       <c r="K31" t="s">
-        <v>103</v>
-      </c>
-      <c r="L31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M31" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="N31">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -2348,7 +2330,7 @@
         <v>2</v>
       </c>
       <c r="R31">
-        <v>11.610310455</v>
+        <v>18.28551888611111</v>
       </c>
     </row>
     <row r="32" spans="1:18">
@@ -2356,7 +2338,7 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s">
         <v>99</v>
@@ -2371,19 +2353,19 @@
         <v>0.3</v>
       </c>
       <c r="G32">
-        <v>2500</v>
+        <v>2700</v>
       </c>
       <c r="H32" s="2">
-        <v>45984.78125</v>
+        <v>45985.98958333334</v>
       </c>
       <c r="I32" s="2">
-        <v>45984.82291666666</v>
+        <v>45986.48958333334</v>
       </c>
       <c r="J32" s="2">
-        <v>45986.02323661984</v>
+        <v>45987.60901629935</v>
       </c>
       <c r="K32" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="M32" t="s">
         <v>102</v>
@@ -2395,13 +2377,13 @@
         <v>0</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R32">
-        <v>29.80767887611111</v>
+        <v>38.86639118444445</v>
       </c>
     </row>
     <row r="33" spans="1:18">
@@ -2409,40 +2391,37 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C33" t="s">
         <v>99</v>
       </c>
       <c r="D33">
-        <v>9.110310455088765</v>
+        <v>9.702185552813946</v>
       </c>
       <c r="E33">
         <v>62.21893992770459</v>
       </c>
       <c r="F33">
-        <v>592.1701795807697</v>
+        <v>630.6420609329065</v>
       </c>
       <c r="G33">
-        <v>2500</v>
+        <v>2700</v>
       </c>
       <c r="H33" s="2">
-        <v>45984.35416666666</v>
+        <v>45982.71908524904</v>
       </c>
       <c r="J33" s="2">
-        <v>45984.83792960229</v>
+        <v>45983.4809818693</v>
       </c>
       <c r="K33" t="s">
-        <v>103</v>
-      </c>
-      <c r="L33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M33" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="N33">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -2454,7 +2433,7 @@
         <v>2</v>
       </c>
       <c r="R33">
-        <v>11.610310455</v>
+        <v>18.28551888611111</v>
       </c>
     </row>
     <row r="34" spans="1:18">
@@ -2462,7 +2441,7 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C34" t="s">
         <v>99</v>
@@ -2480,16 +2459,16 @@
         <v>2500</v>
       </c>
       <c r="H34" s="2">
-        <v>45984.78125</v>
+        <v>45985.98958333334</v>
       </c>
       <c r="I34" s="2">
-        <v>45984.82291666666</v>
+        <v>45986.48958333334</v>
       </c>
       <c r="J34" s="2">
-        <v>45986.02323661984</v>
+        <v>45987.60901629935</v>
       </c>
       <c r="K34" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="M34" t="s">
         <v>102</v>
@@ -2501,13 +2480,13 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R34">
-        <v>29.80767887611111</v>
+        <v>38.86639118444445</v>
       </c>
     </row>
     <row r="35" spans="1:18">
@@ -2515,40 +2494,37 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C35" t="s">
         <v>99</v>
       </c>
       <c r="D35">
-        <v>9.334371213944859</v>
+        <v>9.702185552813946</v>
       </c>
       <c r="E35">
         <v>62.21893992770459</v>
       </c>
       <c r="F35">
-        <v>280.0311364183458</v>
+        <v>630.6420609329065</v>
       </c>
       <c r="G35">
         <v>2500</v>
       </c>
       <c r="H35" s="2">
-        <v>45983.95833333334</v>
+        <v>45982.71908524904</v>
       </c>
       <c r="J35" s="2">
-        <v>45984.84726546724</v>
+        <v>45983.4809818693</v>
       </c>
       <c r="K35" t="s">
         <v>102</v>
       </c>
-      <c r="L35" t="s">
-        <v>103</v>
-      </c>
       <c r="M35" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="N35">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -2560,7 +2536,7 @@
         <v>2</v>
       </c>
       <c r="R35">
-        <v>21.33437121388889</v>
+        <v>18.28551888611111</v>
       </c>
     </row>
     <row r="36" spans="1:18">
@@ -2574,28 +2550,28 @@
         <v>99</v>
       </c>
       <c r="D36">
-        <v>9.334371213944859</v>
+        <v>0.01</v>
       </c>
       <c r="E36">
-        <v>62.21893992770459</v>
+        <v>145</v>
       </c>
       <c r="F36">
-        <v>280.0311364183458</v>
+        <v>0.3</v>
       </c>
       <c r="G36">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="H36" s="2">
-        <v>45983.95833333334</v>
+        <v>45985.98958333334</v>
+      </c>
+      <c r="I36" s="2">
+        <v>45986.48958333334</v>
       </c>
       <c r="J36" s="2">
-        <v>45984.84726546724</v>
+        <v>45987.60901629935</v>
       </c>
       <c r="K36" t="s">
-        <v>102</v>
-      </c>
-      <c r="L36" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M36" t="s">
         <v>102</v>
@@ -2607,13 +2583,13 @@
         <v>0</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R36">
-        <v>21.33437121388889</v>
+        <v>38.86639118444445</v>
       </c>
     </row>
     <row r="37" spans="1:18">
@@ -2621,37 +2597,34 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C37" t="s">
         <v>99</v>
       </c>
       <c r="D37">
-        <v>0.01</v>
+        <v>9.702185552813946</v>
       </c>
       <c r="E37">
-        <v>144</v>
+        <v>62.21893992770459</v>
       </c>
       <c r="F37">
-        <v>0.3</v>
+        <v>630.6420609329065</v>
       </c>
       <c r="G37">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="H37" s="2">
-        <v>45984.92708333334</v>
-      </c>
-      <c r="I37" s="2">
-        <v>45984.98958333334</v>
+        <v>45982.71908524904</v>
       </c>
       <c r="J37" s="2">
-        <v>45986.09673218481</v>
+        <v>45983.4809818693</v>
       </c>
       <c r="K37" t="s">
         <v>102</v>
       </c>
       <c r="M37" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="N37">
         <v>2</v>
@@ -2666,7 +2639,7 @@
         <v>2</v>
       </c>
       <c r="R37">
-        <v>28.07157243555556</v>
+        <v>18.28551888611111</v>
       </c>
     </row>
     <row r="38" spans="1:18">
@@ -2674,52 +2647,52 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C38" t="s">
         <v>99</v>
       </c>
       <c r="D38">
-        <v>9.334371213944859</v>
+        <v>0.01</v>
       </c>
       <c r="E38">
-        <v>62.21893992770459</v>
+        <v>145</v>
       </c>
       <c r="F38">
-        <v>280.0311364183458</v>
+        <v>0.3</v>
       </c>
       <c r="G38">
-        <v>2750</v>
+        <v>3500</v>
       </c>
       <c r="H38" s="2">
-        <v>45983.95833333334</v>
+        <v>45986.28125</v>
+      </c>
+      <c r="I38" s="2">
+        <v>45986.78125</v>
       </c>
       <c r="J38" s="2">
-        <v>45984.84726546724</v>
+        <v>45987.54752008867</v>
       </c>
       <c r="K38" t="s">
-        <v>102</v>
-      </c>
-      <c r="L38" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M38" t="s">
         <v>102</v>
       </c>
       <c r="N38">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R38">
-        <v>21.33437121388889</v>
+        <v>30.39048212805556</v>
       </c>
     </row>
     <row r="39" spans="1:18">
@@ -2727,40 +2700,37 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C39" t="s">
         <v>99</v>
       </c>
       <c r="D39">
-        <v>0.01</v>
+        <v>7.559549950030005</v>
       </c>
       <c r="E39">
-        <v>144</v>
+        <v>62.21893992770459</v>
       </c>
       <c r="F39">
-        <v>0.3</v>
+        <v>226.7864985009002</v>
       </c>
       <c r="G39">
-        <v>2750</v>
+        <v>3500</v>
       </c>
       <c r="H39" s="2">
-        <v>45984.92708333334</v>
-      </c>
-      <c r="I39" s="2">
-        <v>45984.98958333334</v>
+        <v>45984.85416666666</v>
       </c>
       <c r="J39" s="2">
-        <v>45986.09673218481</v>
+        <v>45985.45734235903</v>
       </c>
       <c r="K39" t="s">
         <v>102</v>
       </c>
       <c r="M39" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="N39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -2769,10 +2739,10 @@
         <v>0</v>
       </c>
       <c r="Q39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R39">
-        <v>28.07157243555556</v>
+        <v>14.47621661666667</v>
       </c>
     </row>
     <row r="40" spans="1:18">
@@ -2780,7 +2750,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C40" t="s">
         <v>99</v>
@@ -2795,37 +2765,37 @@
         <v>0.3</v>
       </c>
       <c r="G40">
-        <v>3250</v>
+        <v>2100</v>
       </c>
       <c r="H40" s="2">
-        <v>45988.29166666666</v>
+        <v>45986.28125</v>
       </c>
       <c r="I40" s="2">
-        <v>45988.29166666666</v>
+        <v>45986.78125</v>
       </c>
       <c r="J40" s="2">
-        <v>45989.41390423573</v>
+        <v>45987.54752008867</v>
       </c>
       <c r="K40" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="M40" t="s">
         <v>102</v>
       </c>
       <c r="N40">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q40">
-        <v>102</v>
+        <v>3</v>
       </c>
       <c r="R40">
-        <v>26.9337016575</v>
+        <v>30.39048212805556</v>
       </c>
     </row>
     <row r="41" spans="1:18">
@@ -2833,52 +2803,49 @@
         <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C41" t="s">
         <v>99</v>
       </c>
       <c r="D41">
-        <v>13.03904891423422</v>
+        <v>7.559549950030005</v>
       </c>
       <c r="E41">
         <v>62.21893992770459</v>
       </c>
       <c r="F41">
-        <v>847.5381794252241</v>
+        <v>226.7864985009002</v>
       </c>
       <c r="G41">
-        <v>3250</v>
+        <v>2100</v>
       </c>
       <c r="H41" s="2">
-        <v>45984.9375</v>
+        <v>45984.85416666666</v>
       </c>
       <c r="J41" s="2">
-        <v>45986.11621037142</v>
+        <v>45985.45734235903</v>
       </c>
       <c r="K41" t="s">
         <v>102</v>
       </c>
-      <c r="L41" t="s">
-        <v>103</v>
-      </c>
       <c r="M41" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="N41">
+        <v>1</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
         <v>3</v>
       </c>
-      <c r="O41">
-        <v>0</v>
-      </c>
-      <c r="P41">
-        <v>0</v>
-      </c>
-      <c r="Q41">
-        <v>102</v>
-      </c>
       <c r="R41">
-        <v>28.28904891416667</v>
+        <v>14.47621661666667</v>
       </c>
     </row>
     <row r="42" spans="1:18">
@@ -2886,7 +2853,7 @@
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C42" t="s">
         <v>99</v>
@@ -2901,16 +2868,16 @@
         <v>0.3</v>
       </c>
       <c r="G42">
-        <v>2300</v>
+        <v>2750</v>
       </c>
       <c r="H42" s="2">
-        <v>45988.29166666666</v>
+        <v>45993.01041666666</v>
       </c>
       <c r="I42" s="2">
-        <v>45988.29166666666</v>
+        <v>45993.01041666666</v>
       </c>
       <c r="J42" s="2">
-        <v>45989.41390423573</v>
+        <v>45994.38510101011</v>
       </c>
       <c r="K42" t="s">
         <v>102</v>
@@ -2919,7 +2886,7 @@
         <v>102</v>
       </c>
       <c r="N42">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -2931,7 +2898,7 @@
         <v>102</v>
       </c>
       <c r="R42">
-        <v>26.9337016575</v>
+        <v>32.9924242425</v>
       </c>
     </row>
     <row r="43" spans="1:18">
@@ -2939,7 +2906,7 @@
         <v>38</v>
       </c>
       <c r="B43" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C43" t="s">
         <v>99</v>
@@ -2954,7 +2921,7 @@
         <v>847.5381794252241</v>
       </c>
       <c r="G43">
-        <v>2300</v>
+        <v>2750</v>
       </c>
       <c r="H43" s="2">
         <v>45984.9375</v>
@@ -2992,7 +2959,7 @@
         <v>39</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C44" t="s">
         <v>99</v>
@@ -3007,16 +2974,16 @@
         <v>0.3</v>
       </c>
       <c r="G44">
-        <v>2600</v>
+        <v>50</v>
       </c>
       <c r="H44" s="2">
-        <v>45988.29166666666</v>
+        <v>45993.01041666666</v>
       </c>
       <c r="I44" s="2">
-        <v>45988.29166666666</v>
+        <v>45993.01041666666</v>
       </c>
       <c r="J44" s="2">
-        <v>45989.41390423573</v>
+        <v>45994.38510101011</v>
       </c>
       <c r="K44" t="s">
         <v>102</v>
@@ -3025,7 +2992,7 @@
         <v>102</v>
       </c>
       <c r="N44">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3037,7 +3004,7 @@
         <v>102</v>
       </c>
       <c r="R44">
-        <v>26.9337016575</v>
+        <v>32.9924242425</v>
       </c>
     </row>
     <row r="45" spans="1:18">
@@ -3045,7 +3012,7 @@
         <v>39</v>
       </c>
       <c r="B45" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C45" t="s">
         <v>99</v>
@@ -3060,7 +3027,7 @@
         <v>847.5381794252241</v>
       </c>
       <c r="G45">
-        <v>2600</v>
+        <v>50</v>
       </c>
       <c r="H45" s="2">
         <v>45984.9375</v>
@@ -3107,22 +3074,22 @@
         <v>0.01</v>
       </c>
       <c r="E46">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F46">
         <v>0.3</v>
       </c>
       <c r="G46">
-        <v>1500</v>
+        <v>3150</v>
       </c>
       <c r="H46" s="2">
-        <v>45989.83333333334</v>
+        <v>45993.01041666666</v>
       </c>
       <c r="I46" s="2">
-        <v>45989.83333333334</v>
+        <v>45993.01041666666</v>
       </c>
       <c r="J46" s="2">
-        <v>45991.16837712096</v>
+        <v>45994.38510101011</v>
       </c>
       <c r="K46" t="s">
         <v>102</v>
@@ -3131,7 +3098,7 @@
         <v>102</v>
       </c>
       <c r="N46">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O46">
         <v>0</v>
@@ -3143,7 +3110,7 @@
         <v>102</v>
       </c>
       <c r="R46">
-        <v>32.04105090305556</v>
+        <v>32.9924242425</v>
       </c>
     </row>
     <row r="47" spans="1:18">
@@ -3151,28 +3118,28 @@
         <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C47" t="s">
         <v>99</v>
       </c>
       <c r="D47">
-        <v>13.03904891423422</v>
+        <v>6.769936468817598</v>
       </c>
       <c r="E47">
         <v>62.21893992770459</v>
       </c>
       <c r="F47">
-        <v>847.5381794252241</v>
+        <v>440.0458704731439</v>
       </c>
       <c r="G47">
-        <v>1500</v>
+        <v>3150</v>
       </c>
       <c r="H47" s="2">
-        <v>45984.9375</v>
+        <v>45985.04166666666</v>
       </c>
       <c r="J47" s="2">
-        <v>45986.11621037142</v>
+        <v>45985.68485846398</v>
       </c>
       <c r="K47" t="s">
         <v>102</v>
@@ -3184,7 +3151,7 @@
         <v>102</v>
       </c>
       <c r="N47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O47">
         <v>0</v>
@@ -3196,7 +3163,7 @@
         <v>102</v>
       </c>
       <c r="R47">
-        <v>28.28904891416667</v>
+        <v>15.43660313555556</v>
       </c>
     </row>
     <row r="48" spans="1:18">
@@ -3204,16 +3171,16 @@
         <v>41</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C48" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D48">
         <v>0.01</v>
       </c>
       <c r="E48">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F48">
         <v>0.3</v>
@@ -3222,13 +3189,13 @@
         <v>2250</v>
       </c>
       <c r="H48" s="2">
-        <v>45984.94791666666</v>
+        <v>45993.01041666666</v>
       </c>
       <c r="I48" s="2">
-        <v>45985.01041666666</v>
+        <v>45993.01041666666</v>
       </c>
       <c r="J48" s="2">
-        <v>45986.18150670244</v>
+        <v>45994.38510101011</v>
       </c>
       <c r="K48" t="s">
         <v>102</v>
@@ -3246,10 +3213,10 @@
         <v>0</v>
       </c>
       <c r="Q48">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="R48">
-        <v>29.60616085861111</v>
+        <v>32.9924242425</v>
       </c>
     </row>
     <row r="49" spans="1:18">
@@ -3257,31 +3224,31 @@
         <v>41</v>
       </c>
       <c r="B49" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C49" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D49">
-        <v>11.71486316630421</v>
+        <v>6.769936468817598</v>
       </c>
       <c r="E49">
         <v>62.21893992770459</v>
       </c>
       <c r="F49">
-        <v>761.4661058097738</v>
+        <v>440.0458704731439</v>
       </c>
       <c r="G49">
         <v>2250</v>
       </c>
       <c r="H49" s="2">
-        <v>45984.375</v>
+        <v>45985.04166666666</v>
       </c>
       <c r="J49" s="2">
-        <v>45985.03673040971</v>
+        <v>45985.68485846398</v>
       </c>
       <c r="K49" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L49" t="s">
         <v>103</v>
@@ -3290,7 +3257,7 @@
         <v>102</v>
       </c>
       <c r="N49">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="O49">
         <v>0</v>
@@ -3299,10 +3266,10 @@
         <v>0</v>
       </c>
       <c r="Q49">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="R49">
-        <v>15.88152983305556</v>
+        <v>15.43660313555556</v>
       </c>
     </row>
     <row r="50" spans="1:18">
@@ -3310,7 +3277,7 @@
         <v>42</v>
       </c>
       <c r="B50" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C50" t="s">
         <v>100</v>
@@ -3325,19 +3292,19 @@
         <v>0.3</v>
       </c>
       <c r="G50">
-        <v>3150</v>
+        <v>2900</v>
       </c>
       <c r="H50" s="2">
-        <v>45983.86458333334</v>
+        <v>45984.95833333334</v>
       </c>
       <c r="I50" s="2">
-        <v>45985.01041666666</v>
+        <v>45985</v>
       </c>
       <c r="J50" s="2">
-        <v>45986.12741998743</v>
+        <v>45986.11138281981</v>
       </c>
       <c r="K50" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M50" t="s">
         <v>102</v>
@@ -3349,13 +3316,13 @@
         <v>0</v>
       </c>
       <c r="P50">
-        <v>11.08333333333333</v>
+        <v>0</v>
       </c>
       <c r="Q50">
         <v>2</v>
       </c>
       <c r="R50">
-        <v>54.30807969833334</v>
+        <v>27.67318767555556</v>
       </c>
     </row>
     <row r="51" spans="1:18">
@@ -3369,22 +3336,22 @@
         <v>100</v>
       </c>
       <c r="D51">
-        <v>11.71486316630421</v>
+        <v>11.35842716732944</v>
       </c>
       <c r="E51">
         <v>62.21893992770459</v>
       </c>
       <c r="F51">
-        <v>761.4661058097738</v>
+        <v>738.2977658764135</v>
       </c>
       <c r="G51">
-        <v>3150</v>
+        <v>2900</v>
       </c>
       <c r="H51" s="2">
         <v>45984.375</v>
       </c>
       <c r="J51" s="2">
-        <v>45985.03673040971</v>
+        <v>45985.02187890975</v>
       </c>
       <c r="K51" t="s">
         <v>103</v>
@@ -3408,7 +3375,7 @@
         <v>2</v>
       </c>
       <c r="R51">
-        <v>15.88152983305556</v>
+        <v>15.52509383388889</v>
       </c>
     </row>
     <row r="52" spans="1:18">
@@ -3416,7 +3383,7 @@
         <v>43</v>
       </c>
       <c r="B52" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C52" t="s">
         <v>100</v>
@@ -3434,16 +3401,16 @@
         <v>1800</v>
       </c>
       <c r="H52" s="2">
-        <v>45983.86458333334</v>
+        <v>45984.95833333334</v>
       </c>
       <c r="I52" s="2">
-        <v>45985.01041666666</v>
+        <v>45985</v>
       </c>
       <c r="J52" s="2">
-        <v>45986.12741998743</v>
+        <v>45986.11138281981</v>
       </c>
       <c r="K52" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M52" t="s">
         <v>102</v>
@@ -3455,13 +3422,13 @@
         <v>0</v>
       </c>
       <c r="P52">
-        <v>11.08333333333333</v>
+        <v>0</v>
       </c>
       <c r="Q52">
         <v>2</v>
       </c>
       <c r="R52">
-        <v>54.30807969833334</v>
+        <v>27.67318767555556</v>
       </c>
     </row>
     <row r="53" spans="1:18">
@@ -3475,13 +3442,13 @@
         <v>100</v>
       </c>
       <c r="D53">
-        <v>11.71486316630421</v>
+        <v>11.35842716732944</v>
       </c>
       <c r="E53">
         <v>62.21893992770459</v>
       </c>
       <c r="F53">
-        <v>761.4661058097738</v>
+        <v>738.2977658764135</v>
       </c>
       <c r="G53">
         <v>1800</v>
@@ -3490,7 +3457,7 @@
         <v>45984.375</v>
       </c>
       <c r="J53" s="2">
-        <v>45985.03673040971</v>
+        <v>45985.02187890975</v>
       </c>
       <c r="K53" t="s">
         <v>103</v>
@@ -3514,7 +3481,7 @@
         <v>2</v>
       </c>
       <c r="R53">
-        <v>15.88152983305556</v>
+        <v>15.52509383388889</v>
       </c>
     </row>
     <row r="54" spans="1:18">
@@ -3522,7 +3489,7 @@
         <v>44</v>
       </c>
       <c r="B54" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C54" t="s">
         <v>100</v>
@@ -3537,19 +3504,19 @@
         <v>0.3</v>
       </c>
       <c r="G54">
-        <v>2750</v>
+        <v>2250</v>
       </c>
       <c r="H54" s="2">
-        <v>45983.86458333334</v>
+        <v>45984.95833333334</v>
       </c>
       <c r="I54" s="2">
-        <v>45985.01041666666</v>
+        <v>45985</v>
       </c>
       <c r="J54" s="2">
-        <v>45986.12741998743</v>
+        <v>45986.11138281981</v>
       </c>
       <c r="K54" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M54" t="s">
         <v>102</v>
@@ -3561,13 +3528,13 @@
         <v>0</v>
       </c>
       <c r="P54">
-        <v>11.08333333333333</v>
+        <v>0</v>
       </c>
       <c r="Q54">
         <v>2</v>
       </c>
       <c r="R54">
-        <v>54.30807969833334</v>
+        <v>27.67318767555556</v>
       </c>
     </row>
     <row r="55" spans="1:18">
@@ -3581,22 +3548,22 @@
         <v>100</v>
       </c>
       <c r="D55">
-        <v>11.71486316630421</v>
+        <v>11.35842716732944</v>
       </c>
       <c r="E55">
         <v>62.21893992770459</v>
       </c>
       <c r="F55">
-        <v>761.4661058097738</v>
+        <v>738.2977658764135</v>
       </c>
       <c r="G55">
-        <v>2750</v>
+        <v>2250</v>
       </c>
       <c r="H55" s="2">
         <v>45984.375</v>
       </c>
       <c r="J55" s="2">
-        <v>45985.03673040971</v>
+        <v>45985.02187890975</v>
       </c>
       <c r="K55" t="s">
         <v>103</v>
@@ -3620,7 +3587,7 @@
         <v>2</v>
       </c>
       <c r="R55">
-        <v>15.88152983305556</v>
+        <v>15.52509383388889</v>
       </c>
     </row>
     <row r="56" spans="1:18">
@@ -3628,7 +3595,7 @@
         <v>45</v>
       </c>
       <c r="B56" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C56" t="s">
         <v>100</v>
@@ -3643,37 +3610,37 @@
         <v>0.3</v>
       </c>
       <c r="G56">
-        <v>3150</v>
+        <v>2250</v>
       </c>
       <c r="H56" s="2">
-        <v>45986.125</v>
+        <v>45984.9375</v>
       </c>
       <c r="I56" s="2">
-        <v>45986.625</v>
+        <v>45985</v>
       </c>
       <c r="J56" s="2">
-        <v>45987.5085147962</v>
+        <v>45986.27135156703</v>
       </c>
       <c r="K56" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="M56" t="s">
         <v>102</v>
       </c>
       <c r="N56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O56">
         <v>0</v>
       </c>
       <c r="P56">
-        <v>12.08333333333333</v>
+        <v>0</v>
       </c>
       <c r="Q56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R56">
-        <v>33.20435510888889</v>
+        <v>32.01243760861111</v>
       </c>
     </row>
     <row r="57" spans="1:18">
@@ -3687,22 +3654,22 @@
         <v>100</v>
       </c>
       <c r="D57">
-        <v>11.71486316630421</v>
+        <v>11.35842716732944</v>
       </c>
       <c r="E57">
         <v>62.21893992770459</v>
       </c>
       <c r="F57">
-        <v>761.4661058097738</v>
+        <v>738.2977658764135</v>
       </c>
       <c r="G57">
-        <v>3150</v>
+        <v>2250</v>
       </c>
       <c r="H57" s="2">
         <v>45984.375</v>
       </c>
       <c r="J57" s="2">
-        <v>45985.03673040971</v>
+        <v>45985.02187890975</v>
       </c>
       <c r="K57" t="s">
         <v>103</v>
@@ -3726,7 +3693,7 @@
         <v>2</v>
       </c>
       <c r="R57">
-        <v>15.88152983305556</v>
+        <v>15.52509383388889</v>
       </c>
     </row>
     <row r="58" spans="1:18">
@@ -3749,16 +3716,16 @@
         <v>0.3</v>
       </c>
       <c r="G58">
-        <v>2200</v>
+        <v>3150</v>
       </c>
       <c r="H58" s="2">
-        <v>45984.92708333334</v>
+        <v>45984.9375</v>
       </c>
       <c r="I58" s="2">
-        <v>45984.98958333334</v>
+        <v>45985</v>
       </c>
       <c r="J58" s="2">
-        <v>45986.09673218481</v>
+        <v>45986.27135156703</v>
       </c>
       <c r="K58" t="s">
         <v>102</v>
@@ -3779,7 +3746,7 @@
         <v>2</v>
       </c>
       <c r="R58">
-        <v>28.07157243555556</v>
+        <v>32.01243760861111</v>
       </c>
     </row>
     <row r="59" spans="1:18">
@@ -3787,31 +3754,31 @@
         <v>46</v>
       </c>
       <c r="B59" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C59" t="s">
         <v>100</v>
       </c>
       <c r="D59">
-        <v>11.11052498709011</v>
+        <v>11.35842716732944</v>
       </c>
       <c r="E59">
         <v>62.21893992770459</v>
       </c>
       <c r="F59">
-        <v>722.1841241608569</v>
+        <v>738.2977658764135</v>
       </c>
       <c r="G59">
-        <v>2200</v>
+        <v>3150</v>
       </c>
       <c r="H59" s="2">
-        <v>45984.20833333334</v>
+        <v>45984.375</v>
       </c>
       <c r="J59" s="2">
-        <v>45985.01154965225</v>
+        <v>45985.02187890975</v>
       </c>
       <c r="K59" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="L59" t="s">
         <v>103</v>
@@ -3832,7 +3799,7 @@
         <v>2</v>
       </c>
       <c r="R59">
-        <v>19.27719165388889</v>
+        <v>15.52509383388889</v>
       </c>
     </row>
     <row r="60" spans="1:18">
@@ -3855,16 +3822,16 @@
         <v>0.3</v>
       </c>
       <c r="G60">
-        <v>2100</v>
+        <v>3100</v>
       </c>
       <c r="H60" s="2">
-        <v>45984.92708333334</v>
+        <v>45984.9375</v>
       </c>
       <c r="I60" s="2">
-        <v>45984.98958333334</v>
+        <v>45985</v>
       </c>
       <c r="J60" s="2">
-        <v>45986.09673218481</v>
+        <v>45986.27135156703</v>
       </c>
       <c r="K60" t="s">
         <v>102</v>
@@ -3885,7 +3852,7 @@
         <v>2</v>
       </c>
       <c r="R60">
-        <v>28.07157243555556</v>
+        <v>32.01243760861111</v>
       </c>
     </row>
     <row r="61" spans="1:18">
@@ -3899,25 +3866,25 @@
         <v>100</v>
       </c>
       <c r="D61">
-        <v>11.11052498709011</v>
+        <v>10.79467394230661</v>
       </c>
       <c r="E61">
         <v>62.21893992770459</v>
       </c>
       <c r="F61">
-        <v>722.1841241608569</v>
+        <v>323.8402182691982</v>
       </c>
       <c r="G61">
-        <v>2100</v>
+        <v>3100</v>
       </c>
       <c r="H61" s="2">
-        <v>45984.20833333334</v>
+        <v>45983.95833333334</v>
       </c>
       <c r="J61" s="2">
-        <v>45985.01154965225</v>
+        <v>45984.93241696982</v>
       </c>
       <c r="K61" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="L61" t="s">
         <v>103</v>
@@ -3926,7 +3893,7 @@
         <v>102</v>
       </c>
       <c r="N61">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -3938,7 +3905,7 @@
         <v>2</v>
       </c>
       <c r="R61">
-        <v>19.27719165388889</v>
+        <v>23.37800727555555</v>
       </c>
     </row>
     <row r="62" spans="1:18">
@@ -3946,7 +3913,7 @@
         <v>48</v>
       </c>
       <c r="B62" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C62" t="s">
         <v>100</v>
@@ -3961,16 +3928,16 @@
         <v>0.3</v>
       </c>
       <c r="G62">
-        <v>3000</v>
+        <v>3150</v>
       </c>
       <c r="H62" s="2">
-        <v>45984.92708333334</v>
+        <v>45984.9375</v>
       </c>
       <c r="I62" s="2">
-        <v>45984.98958333334</v>
+        <v>45985</v>
       </c>
       <c r="J62" s="2">
-        <v>45986.20609383736</v>
+        <v>45986.27135156703</v>
       </c>
       <c r="K62" t="s">
         <v>102</v>
@@ -3991,7 +3958,7 @@
         <v>2</v>
       </c>
       <c r="R62">
-        <v>30.69625209666667</v>
+        <v>32.01243760861111</v>
       </c>
     </row>
     <row r="63" spans="1:18">
@@ -4005,25 +3972,25 @@
         <v>100</v>
       </c>
       <c r="D63">
-        <v>11.11052498709011</v>
+        <v>10.79467394230661</v>
       </c>
       <c r="E63">
         <v>62.21893992770459</v>
       </c>
       <c r="F63">
-        <v>722.1841241608569</v>
+        <v>323.8402182691982</v>
       </c>
       <c r="G63">
-        <v>3000</v>
+        <v>3150</v>
       </c>
       <c r="H63" s="2">
-        <v>45984.20833333334</v>
+        <v>45983.95833333334</v>
       </c>
       <c r="J63" s="2">
-        <v>45985.01154965225</v>
+        <v>45984.93241696982</v>
       </c>
       <c r="K63" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="L63" t="s">
         <v>103</v>
@@ -4032,7 +3999,7 @@
         <v>102</v>
       </c>
       <c r="N63">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -4044,7 +4011,7 @@
         <v>2</v>
       </c>
       <c r="R63">
-        <v>19.27719165388889</v>
+        <v>23.37800727555555</v>
       </c>
     </row>
     <row r="64" spans="1:18">
@@ -4070,13 +4037,13 @@
         <v>2250</v>
       </c>
       <c r="H64" s="2">
-        <v>45984.92708333334</v>
+        <v>45984.84375</v>
       </c>
       <c r="I64" s="2">
-        <v>45984.98958333334</v>
+        <v>45984.90625</v>
       </c>
       <c r="J64" s="2">
-        <v>45986.20609383736</v>
+        <v>45986.20064948804</v>
       </c>
       <c r="K64" t="s">
         <v>102</v>
@@ -4097,7 +4064,7 @@
         <v>2</v>
       </c>
       <c r="R64">
-        <v>30.69625209666667</v>
+        <v>32.56558771305556</v>
       </c>
     </row>
     <row r="65" spans="1:18">
@@ -4111,25 +4078,25 @@
         <v>100</v>
       </c>
       <c r="D65">
-        <v>11.11052498709011</v>
+        <v>10.79467394230661</v>
       </c>
       <c r="E65">
         <v>62.21893992770459</v>
       </c>
       <c r="F65">
-        <v>722.1841241608569</v>
+        <v>323.8402182691982</v>
       </c>
       <c r="G65">
         <v>2250</v>
       </c>
       <c r="H65" s="2">
-        <v>45984.20833333334</v>
+        <v>45983.95833333334</v>
       </c>
       <c r="J65" s="2">
-        <v>45985.01154965225</v>
+        <v>45984.93241696982</v>
       </c>
       <c r="K65" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="L65" t="s">
         <v>103</v>
@@ -4138,7 +4105,7 @@
         <v>102</v>
       </c>
       <c r="N65">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -4150,7 +4117,7 @@
         <v>2</v>
       </c>
       <c r="R65">
-        <v>19.27719165388889</v>
+        <v>23.37800727555555</v>
       </c>
     </row>
     <row r="66" spans="1:18">
@@ -4173,16 +4140,16 @@
         <v>0.3</v>
       </c>
       <c r="G66">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="H66" s="2">
-        <v>45984.92708333334</v>
+        <v>45984.84375</v>
       </c>
       <c r="I66" s="2">
-        <v>45984.98958333334</v>
+        <v>45984.90625</v>
       </c>
       <c r="J66" s="2">
-        <v>45986.20609383736</v>
+        <v>45986.20064948804</v>
       </c>
       <c r="K66" t="s">
         <v>102</v>
@@ -4203,7 +4170,7 @@
         <v>2</v>
       </c>
       <c r="R66">
-        <v>30.69625209666667</v>
+        <v>32.56558771305556</v>
       </c>
     </row>
     <row r="67" spans="1:18">
@@ -4217,25 +4184,25 @@
         <v>100</v>
       </c>
       <c r="D67">
-        <v>11.11052498709011</v>
+        <v>10.79467394230661</v>
       </c>
       <c r="E67">
         <v>62.21893992770459</v>
       </c>
       <c r="F67">
-        <v>722.1841241608569</v>
+        <v>323.8402182691982</v>
       </c>
       <c r="G67">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="H67" s="2">
-        <v>45984.20833333334</v>
+        <v>45983.95833333334</v>
       </c>
       <c r="J67" s="2">
-        <v>45985.01154965225</v>
+        <v>45984.93241696982</v>
       </c>
       <c r="K67" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="L67" t="s">
         <v>103</v>
@@ -4244,7 +4211,7 @@
         <v>102</v>
       </c>
       <c r="N67">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O67">
         <v>0</v>
@@ -4256,7 +4223,7 @@
         <v>2</v>
       </c>
       <c r="R67">
-        <v>19.27719165388889</v>
+        <v>23.37800727555555</v>
       </c>
     </row>
     <row r="68" spans="1:18">
@@ -4279,16 +4246,16 @@
         <v>0.3</v>
       </c>
       <c r="G68">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="H68" s="2">
-        <v>45984.92708333334</v>
+        <v>45984.84375</v>
       </c>
       <c r="I68" s="2">
-        <v>45984.98958333334</v>
+        <v>45984.90625</v>
       </c>
       <c r="J68" s="2">
-        <v>45986.20609383736</v>
+        <v>45986.20064948804</v>
       </c>
       <c r="K68" t="s">
         <v>102</v>
@@ -4309,7 +4276,7 @@
         <v>2</v>
       </c>
       <c r="R68">
-        <v>30.69625209666667</v>
+        <v>32.56558771305556</v>
       </c>
     </row>
     <row r="69" spans="1:18">
@@ -4317,34 +4284,37 @@
         <v>51</v>
       </c>
       <c r="B69" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C69" t="s">
         <v>100</v>
       </c>
       <c r="D69">
-        <v>10.70374352527781</v>
+        <v>9.967111735991512</v>
       </c>
       <c r="E69">
         <v>62.21893992770459</v>
       </c>
       <c r="F69">
-        <v>695.7433291430575</v>
+        <v>647.8622628394482</v>
       </c>
       <c r="G69">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="H69" s="2">
-        <v>45982.71908524904</v>
+        <v>45984.375</v>
       </c>
       <c r="J69" s="2">
-        <v>45983.52271345148</v>
+        <v>45984.92918521123</v>
       </c>
       <c r="K69" t="s">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="L69" t="s">
+        <v>103</v>
       </c>
       <c r="M69" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="N69">
         <v>2</v>
@@ -4359,7 +4329,7 @@
         <v>2</v>
       </c>
       <c r="R69">
-        <v>19.28707685861111</v>
+        <v>13.30044506944444</v>
       </c>
     </row>
     <row r="70" spans="1:18">
@@ -4367,7 +4337,7 @@
         <v>52</v>
       </c>
       <c r="B70" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C70" t="s">
         <v>100</v>
@@ -4382,16 +4352,16 @@
         <v>0.3</v>
       </c>
       <c r="G70">
-        <v>3300</v>
+        <v>4750</v>
       </c>
       <c r="H70" s="2">
-        <v>45984.94791666666</v>
+        <v>45984.84375</v>
       </c>
       <c r="I70" s="2">
-        <v>45985.01041666666</v>
+        <v>45984.90625</v>
       </c>
       <c r="J70" s="2">
-        <v>45986.18150670244</v>
+        <v>45986.20064948804</v>
       </c>
       <c r="K70" t="s">
         <v>102</v>
@@ -4412,7 +4382,7 @@
         <v>2</v>
       </c>
       <c r="R70">
-        <v>29.60616085861111</v>
+        <v>32.56558771305556</v>
       </c>
     </row>
     <row r="71" spans="1:18">
@@ -4420,34 +4390,37 @@
         <v>52</v>
       </c>
       <c r="B71" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C71" t="s">
         <v>100</v>
       </c>
       <c r="D71">
-        <v>10.70374352527781</v>
+        <v>9.967111735991512</v>
       </c>
       <c r="E71">
         <v>62.21893992770459</v>
       </c>
       <c r="F71">
-        <v>695.7433291430575</v>
+        <v>647.8622628394482</v>
       </c>
       <c r="G71">
-        <v>3300</v>
+        <v>4750</v>
       </c>
       <c r="H71" s="2">
-        <v>45982.71908524904</v>
+        <v>45984.375</v>
       </c>
       <c r="J71" s="2">
-        <v>45983.52271345148</v>
+        <v>45984.92918521123</v>
       </c>
       <c r="K71" t="s">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="L71" t="s">
+        <v>103</v>
       </c>
       <c r="M71" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="N71">
         <v>2</v>
@@ -4462,7 +4435,7 @@
         <v>2</v>
       </c>
       <c r="R71">
-        <v>19.28707685861111</v>
+        <v>13.30044506944444</v>
       </c>
     </row>
     <row r="72" spans="1:18">
@@ -4470,7 +4443,7 @@
         <v>53</v>
       </c>
       <c r="B72" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C72" t="s">
         <v>100</v>
@@ -4485,16 +4458,16 @@
         <v>0.3</v>
       </c>
       <c r="G72">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="H72" s="2">
-        <v>45984.94791666666</v>
+        <v>45984.86458333334</v>
       </c>
       <c r="I72" s="2">
-        <v>45985.01041666666</v>
+        <v>45984.90625</v>
       </c>
       <c r="J72" s="2">
-        <v>45986.18150670244</v>
+        <v>45985.98400122854</v>
       </c>
       <c r="K72" t="s">
         <v>102</v>
@@ -4503,7 +4476,7 @@
         <v>102</v>
       </c>
       <c r="N72">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4515,7 +4488,7 @@
         <v>2</v>
       </c>
       <c r="R72">
-        <v>29.60616085861111</v>
+        <v>26.866029485</v>
       </c>
     </row>
     <row r="73" spans="1:18">
@@ -4523,34 +4496,37 @@
         <v>53</v>
       </c>
       <c r="B73" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C73" t="s">
         <v>100</v>
       </c>
       <c r="D73">
-        <v>10.70374352527781</v>
+        <v>9.967111735991512</v>
       </c>
       <c r="E73">
         <v>62.21893992770459</v>
       </c>
       <c r="F73">
-        <v>695.7433291430575</v>
+        <v>647.8622628394482</v>
       </c>
       <c r="G73">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="H73" s="2">
-        <v>45982.71908524904</v>
+        <v>45984.375</v>
       </c>
       <c r="J73" s="2">
-        <v>45983.52271345148</v>
+        <v>45984.92918521123</v>
       </c>
       <c r="K73" t="s">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="L73" t="s">
+        <v>103</v>
       </c>
       <c r="M73" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="N73">
         <v>2</v>
@@ -4565,7 +4541,7 @@
         <v>2</v>
       </c>
       <c r="R73">
-        <v>19.28707685861111</v>
+        <v>13.30044506944444</v>
       </c>
     </row>
     <row r="74" spans="1:18">
@@ -4573,7 +4549,7 @@
         <v>54</v>
       </c>
       <c r="B74" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C74" t="s">
         <v>100</v>
@@ -4591,13 +4567,13 @@
         <v>2250</v>
       </c>
       <c r="H74" s="2">
-        <v>45984.94791666666</v>
+        <v>45984.86458333334</v>
       </c>
       <c r="I74" s="2">
-        <v>45985.01041666666</v>
+        <v>45984.90625</v>
       </c>
       <c r="J74" s="2">
-        <v>45986.18150670244</v>
+        <v>45985.98400122854</v>
       </c>
       <c r="K74" t="s">
         <v>102</v>
@@ -4606,7 +4582,7 @@
         <v>102</v>
       </c>
       <c r="N74">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O74">
         <v>0</v>
@@ -4618,7 +4594,7 @@
         <v>2</v>
       </c>
       <c r="R74">
-        <v>29.60616085861111</v>
+        <v>26.866029485</v>
       </c>
     </row>
     <row r="75" spans="1:18">
@@ -4626,34 +4602,37 @@
         <v>54</v>
       </c>
       <c r="B75" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C75" t="s">
         <v>100</v>
       </c>
       <c r="D75">
-        <v>10.70374352527781</v>
+        <v>9.967111735991512</v>
       </c>
       <c r="E75">
         <v>62.21893992770459</v>
       </c>
       <c r="F75">
-        <v>695.7433291430575</v>
+        <v>647.8622628394482</v>
       </c>
       <c r="G75">
         <v>2250</v>
       </c>
       <c r="H75" s="2">
-        <v>45982.71908524904</v>
+        <v>45984.375</v>
       </c>
       <c r="J75" s="2">
-        <v>45983.52271345148</v>
+        <v>45984.92918521123</v>
       </c>
       <c r="K75" t="s">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="L75" t="s">
+        <v>103</v>
       </c>
       <c r="M75" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="N75">
         <v>2</v>
@@ -4668,7 +4647,7 @@
         <v>2</v>
       </c>
       <c r="R75">
-        <v>19.28707685861111</v>
+        <v>13.30044506944444</v>
       </c>
     </row>
     <row r="76" spans="1:18">
@@ -4676,7 +4655,7 @@
         <v>55</v>
       </c>
       <c r="B76" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C76" t="s">
         <v>100</v>
@@ -4691,37 +4670,37 @@
         <v>0.3</v>
       </c>
       <c r="G76">
-        <v>3150</v>
+        <v>2250</v>
       </c>
       <c r="H76" s="2">
-        <v>45986.125</v>
+        <v>45984.86458333334</v>
       </c>
       <c r="I76" s="2">
-        <v>45986.625</v>
+        <v>45984.90625</v>
       </c>
       <c r="J76" s="2">
-        <v>45987.5085147962</v>
+        <v>45985.98400122854</v>
       </c>
       <c r="K76" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="M76" t="s">
         <v>102</v>
       </c>
       <c r="N76">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O76">
         <v>0</v>
       </c>
       <c r="P76">
-        <v>12.08333333333333</v>
+        <v>0</v>
       </c>
       <c r="Q76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R76">
-        <v>33.20435510888889</v>
+        <v>26.866029485</v>
       </c>
     </row>
     <row r="77" spans="1:18">
@@ -4729,37 +4708,40 @@
         <v>55</v>
       </c>
       <c r="B77" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C77" t="s">
         <v>100</v>
       </c>
       <c r="D77">
-        <v>9.702185552813946</v>
+        <v>9.110310455088765</v>
       </c>
       <c r="E77">
         <v>62.21893992770459</v>
       </c>
       <c r="F77">
-        <v>630.6420609329065</v>
+        <v>592.1701795807697</v>
       </c>
       <c r="G77">
-        <v>3150</v>
+        <v>2250</v>
       </c>
       <c r="H77" s="2">
-        <v>45982.71908524904</v>
+        <v>45984.35416666666</v>
       </c>
       <c r="J77" s="2">
-        <v>45983.4809818693</v>
+        <v>45984.83792960229</v>
       </c>
       <c r="K77" t="s">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="L77" t="s">
+        <v>103</v>
       </c>
       <c r="M77" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="N77">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O77">
         <v>0</v>
@@ -4771,7 +4753,7 @@
         <v>2</v>
       </c>
       <c r="R77">
-        <v>18.28551888611111</v>
+        <v>11.610310455</v>
       </c>
     </row>
     <row r="78" spans="1:18">
@@ -4779,7 +4761,7 @@
         <v>56</v>
       </c>
       <c r="B78" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C78" t="s">
         <v>100</v>
@@ -4794,19 +4776,19 @@
         <v>0.3</v>
       </c>
       <c r="G78">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="H78" s="2">
-        <v>45986</v>
+        <v>45984.78125</v>
       </c>
       <c r="I78" s="2">
-        <v>45986.5</v>
+        <v>45984.82291666666</v>
       </c>
       <c r="J78" s="2">
-        <v>45987.61243112948</v>
+        <v>45986.01578047948</v>
       </c>
       <c r="K78" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="M78" t="s">
         <v>102</v>
@@ -4818,13 +4800,13 @@
         <v>0</v>
       </c>
       <c r="P78">
-        <v>12.08333333333333</v>
+        <v>0</v>
       </c>
       <c r="Q78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R78">
-        <v>38.6983471075</v>
+        <v>29.6287315075</v>
       </c>
     </row>
     <row r="79" spans="1:18">
@@ -4832,37 +4814,40 @@
         <v>56</v>
       </c>
       <c r="B79" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C79" t="s">
         <v>100</v>
       </c>
       <c r="D79">
-        <v>9.702185552813946</v>
+        <v>9.110310455088765</v>
       </c>
       <c r="E79">
         <v>62.21893992770459</v>
       </c>
       <c r="F79">
-        <v>630.6420609329065</v>
+        <v>592.1701795807697</v>
       </c>
       <c r="G79">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="H79" s="2">
-        <v>45982.71908524904</v>
+        <v>45984.35416666666</v>
       </c>
       <c r="J79" s="2">
-        <v>45983.4809818693</v>
+        <v>45984.83792960229</v>
       </c>
       <c r="K79" t="s">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="L79" t="s">
+        <v>103</v>
       </c>
       <c r="M79" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="N79">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O79">
         <v>0</v>
@@ -4874,7 +4859,7 @@
         <v>2</v>
       </c>
       <c r="R79">
-        <v>18.28551888611111</v>
+        <v>11.610310455</v>
       </c>
     </row>
     <row r="80" spans="1:18">
@@ -4882,7 +4867,7 @@
         <v>57</v>
       </c>
       <c r="B80" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C80" t="s">
         <v>100</v>
@@ -4900,16 +4885,16 @@
         <v>2500</v>
       </c>
       <c r="H80" s="2">
-        <v>45986</v>
+        <v>45984.78125</v>
       </c>
       <c r="I80" s="2">
-        <v>45986.5</v>
+        <v>45984.82291666666</v>
       </c>
       <c r="J80" s="2">
-        <v>45987.61243112948</v>
+        <v>45986.01578047948</v>
       </c>
       <c r="K80" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="M80" t="s">
         <v>102</v>
@@ -4921,13 +4906,13 @@
         <v>0</v>
       </c>
       <c r="P80">
-        <v>12.08333333333333</v>
+        <v>0</v>
       </c>
       <c r="Q80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R80">
-        <v>38.6983471075</v>
+        <v>29.6287315075</v>
       </c>
     </row>
     <row r="81" spans="1:18">
@@ -4935,37 +4920,40 @@
         <v>57</v>
       </c>
       <c r="B81" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C81" t="s">
         <v>100</v>
       </c>
       <c r="D81">
-        <v>9.702185552813946</v>
+        <v>9.110310455088765</v>
       </c>
       <c r="E81">
         <v>62.21893992770459</v>
       </c>
       <c r="F81">
-        <v>630.6420609329065</v>
+        <v>592.1701795807697</v>
       </c>
       <c r="G81">
         <v>2500</v>
       </c>
       <c r="H81" s="2">
-        <v>45982.71908524904</v>
+        <v>45984.35416666666</v>
       </c>
       <c r="J81" s="2">
-        <v>45983.4809818693</v>
+        <v>45984.83792960229</v>
       </c>
       <c r="K81" t="s">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="L81" t="s">
+        <v>103</v>
       </c>
       <c r="M81" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="N81">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O81">
         <v>0</v>
@@ -4977,7 +4965,7 @@
         <v>2</v>
       </c>
       <c r="R81">
-        <v>18.28551888611111</v>
+        <v>11.610310455</v>
       </c>
     </row>
     <row r="82" spans="1:18">
@@ -4985,7 +4973,7 @@
         <v>58</v>
       </c>
       <c r="B82" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C82" t="s">
         <v>100</v>
@@ -5000,19 +4988,19 @@
         <v>0.3</v>
       </c>
       <c r="G82">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="H82" s="2">
-        <v>45986</v>
+        <v>45984.78125</v>
       </c>
       <c r="I82" s="2">
-        <v>45986.5</v>
+        <v>45984.82291666666</v>
       </c>
       <c r="J82" s="2">
-        <v>45987.61243112948</v>
+        <v>45986.01578047948</v>
       </c>
       <c r="K82" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="M82" t="s">
         <v>102</v>
@@ -5024,13 +5012,13 @@
         <v>0</v>
       </c>
       <c r="P82">
-        <v>12.08333333333333</v>
+        <v>0</v>
       </c>
       <c r="Q82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R82">
-        <v>38.6983471075</v>
+        <v>29.6287315075</v>
       </c>
     </row>
     <row r="83" spans="1:18">
@@ -5038,37 +5026,40 @@
         <v>58</v>
       </c>
       <c r="B83" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C83" t="s">
         <v>100</v>
       </c>
       <c r="D83">
-        <v>9.702185552813946</v>
+        <v>9.334371213944859</v>
       </c>
       <c r="E83">
         <v>62.21893992770459</v>
       </c>
       <c r="F83">
-        <v>630.6420609329065</v>
+        <v>280.0311364183458</v>
       </c>
       <c r="G83">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="H83" s="2">
-        <v>45982.71908524904</v>
+        <v>45983.95833333334</v>
       </c>
       <c r="J83" s="2">
-        <v>45983.4809818693</v>
+        <v>45984.84726546724</v>
       </c>
       <c r="K83" t="s">
         <v>102</v>
       </c>
+      <c r="L83" t="s">
+        <v>103</v>
+      </c>
       <c r="M83" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="N83">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O83">
         <v>0</v>
@@ -5080,7 +5071,7 @@
         <v>2</v>
       </c>
       <c r="R83">
-        <v>18.28551888611111</v>
+        <v>21.33437121388889</v>
       </c>
     </row>
     <row r="84" spans="1:18">
@@ -5088,52 +5079,52 @@
         <v>59</v>
       </c>
       <c r="B84" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C84" t="s">
         <v>100</v>
       </c>
       <c r="D84">
-        <v>0.01</v>
+        <v>9.334371213944859</v>
       </c>
       <c r="E84">
-        <v>144</v>
+        <v>62.21893992770459</v>
       </c>
       <c r="F84">
-        <v>0.3</v>
+        <v>280.0311364183458</v>
       </c>
       <c r="G84">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="H84" s="2">
-        <v>45986.20833333334</v>
-      </c>
-      <c r="I84" s="2">
-        <v>45986.70833333334</v>
+        <v>45983.95833333334</v>
       </c>
       <c r="J84" s="2">
-        <v>45987.47235905856</v>
+        <v>45984.84726546724</v>
       </c>
       <c r="K84" t="s">
-        <v>107</v>
+        <v>102</v>
+      </c>
+      <c r="L84" t="s">
+        <v>103</v>
       </c>
       <c r="M84" t="s">
         <v>102</v>
       </c>
       <c r="N84">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O84">
         <v>0</v>
       </c>
       <c r="P84">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q84">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R84">
-        <v>30.33661740555556</v>
+        <v>21.33437121388889</v>
       </c>
     </row>
     <row r="85" spans="1:18">
@@ -5141,37 +5132,40 @@
         <v>59</v>
       </c>
       <c r="B85" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C85" t="s">
         <v>100</v>
       </c>
       <c r="D85">
-        <v>7.559549950030005</v>
+        <v>0.01</v>
       </c>
       <c r="E85">
-        <v>62.21893992770459</v>
+        <v>144</v>
       </c>
       <c r="F85">
-        <v>226.7864985009002</v>
+        <v>0.3</v>
       </c>
       <c r="G85">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="H85" s="2">
-        <v>45984.85416666666</v>
+        <v>45984.92708333334</v>
+      </c>
+      <c r="I85" s="2">
+        <v>45984.98958333334</v>
       </c>
       <c r="J85" s="2">
-        <v>45985.45734235903</v>
+        <v>45986.09673218481</v>
       </c>
       <c r="K85" t="s">
         <v>102</v>
       </c>
       <c r="M85" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="N85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O85">
         <v>0</v>
@@ -5180,10 +5174,10 @@
         <v>0</v>
       </c>
       <c r="Q85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R85">
-        <v>14.47621661666667</v>
+        <v>28.07157243555556</v>
       </c>
     </row>
     <row r="86" spans="1:18">
@@ -5191,52 +5185,52 @@
         <v>60</v>
       </c>
       <c r="B86" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C86" t="s">
         <v>100</v>
       </c>
       <c r="D86">
-        <v>0.01</v>
+        <v>9.334371213944859</v>
       </c>
       <c r="E86">
-        <v>144</v>
+        <v>62.21893992770459</v>
       </c>
       <c r="F86">
-        <v>0.3</v>
+        <v>280.0311364183458</v>
       </c>
       <c r="G86">
-        <v>2100</v>
+        <v>2750</v>
       </c>
       <c r="H86" s="2">
-        <v>45986.20833333334</v>
-      </c>
-      <c r="I86" s="2">
-        <v>45986.70833333334</v>
+        <v>45983.95833333334</v>
       </c>
       <c r="J86" s="2">
-        <v>45987.47235905856</v>
+        <v>45984.84726546724</v>
       </c>
       <c r="K86" t="s">
-        <v>107</v>
+        <v>102</v>
+      </c>
+      <c r="L86" t="s">
+        <v>103</v>
       </c>
       <c r="M86" t="s">
         <v>102</v>
       </c>
       <c r="N86">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O86">
         <v>0</v>
       </c>
       <c r="P86">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R86">
-        <v>30.33661740555556</v>
+        <v>21.33437121388889</v>
       </c>
     </row>
     <row r="87" spans="1:18">
@@ -5244,37 +5238,40 @@
         <v>60</v>
       </c>
       <c r="B87" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C87" t="s">
         <v>100</v>
       </c>
       <c r="D87">
-        <v>7.559549950030005</v>
+        <v>0.01</v>
       </c>
       <c r="E87">
-        <v>62.21893992770459</v>
+        <v>144</v>
       </c>
       <c r="F87">
-        <v>226.7864985009002</v>
+        <v>0.3</v>
       </c>
       <c r="G87">
-        <v>2100</v>
+        <v>2750</v>
       </c>
       <c r="H87" s="2">
-        <v>45984.85416666666</v>
+        <v>45984.92708333334</v>
+      </c>
+      <c r="I87" s="2">
+        <v>45984.98958333334</v>
       </c>
       <c r="J87" s="2">
-        <v>45985.45734235903</v>
+        <v>45986.09673218481</v>
       </c>
       <c r="K87" t="s">
         <v>102</v>
       </c>
       <c r="M87" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="N87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O87">
         <v>0</v>
@@ -5283,10 +5280,10 @@
         <v>0</v>
       </c>
       <c r="Q87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R87">
-        <v>14.47621661666667</v>
+        <v>28.07157243555556</v>
       </c>
     </row>
     <row r="88" spans="1:18">
@@ -5294,7 +5291,7 @@
         <v>61</v>
       </c>
       <c r="B88" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C88" t="s">
         <v>100</v>
@@ -5309,16 +5306,16 @@
         <v>0.3</v>
       </c>
       <c r="G88">
-        <v>2750</v>
+        <v>3250</v>
       </c>
       <c r="H88" s="2">
-        <v>45989.83333333334</v>
+        <v>45989.53125</v>
       </c>
       <c r="I88" s="2">
-        <v>45989.83333333334</v>
+        <v>45989.53125</v>
       </c>
       <c r="J88" s="2">
-        <v>45991.16837712096</v>
+        <v>45990.68444318017</v>
       </c>
       <c r="K88" t="s">
         <v>102</v>
@@ -5327,7 +5324,7 @@
         <v>102</v>
       </c>
       <c r="N88">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O88">
         <v>0</v>
@@ -5339,7 +5336,7 @@
         <v>102</v>
       </c>
       <c r="R88">
-        <v>32.04105090305556</v>
+        <v>27.67663632416667</v>
       </c>
     </row>
     <row r="89" spans="1:18">
@@ -5347,7 +5344,7 @@
         <v>61</v>
       </c>
       <c r="B89" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C89" t="s">
         <v>100</v>
@@ -5362,7 +5359,7 @@
         <v>847.5381794252241</v>
       </c>
       <c r="G89">
-        <v>2750</v>
+        <v>3250</v>
       </c>
       <c r="H89" s="2">
         <v>45984.9375</v>
@@ -5400,7 +5397,7 @@
         <v>62</v>
       </c>
       <c r="B90" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C90" t="s">
         <v>100</v>
@@ -5415,16 +5412,16 @@
         <v>0.3</v>
       </c>
       <c r="G90">
-        <v>50</v>
+        <v>2300</v>
       </c>
       <c r="H90" s="2">
-        <v>45989.83333333334</v>
+        <v>45989.53125</v>
       </c>
       <c r="I90" s="2">
-        <v>45989.83333333334</v>
+        <v>45989.53125</v>
       </c>
       <c r="J90" s="2">
-        <v>45991.16837712096</v>
+        <v>45990.68444318017</v>
       </c>
       <c r="K90" t="s">
         <v>102</v>
@@ -5433,7 +5430,7 @@
         <v>102</v>
       </c>
       <c r="N90">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O90">
         <v>0</v>
@@ -5445,7 +5442,7 @@
         <v>102</v>
       </c>
       <c r="R90">
-        <v>32.04105090305556</v>
+        <v>27.67663632416667</v>
       </c>
     </row>
     <row r="91" spans="1:18">
@@ -5453,7 +5450,7 @@
         <v>62</v>
       </c>
       <c r="B91" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C91" t="s">
         <v>100</v>
@@ -5468,7 +5465,7 @@
         <v>847.5381794252241</v>
       </c>
       <c r="G91">
-        <v>50</v>
+        <v>2300</v>
       </c>
       <c r="H91" s="2">
         <v>45984.9375</v>
@@ -5506,7 +5503,7 @@
         <v>63</v>
       </c>
       <c r="B92" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C92" t="s">
         <v>100</v>
@@ -5521,16 +5518,16 @@
         <v>0.3</v>
       </c>
       <c r="G92">
-        <v>3150</v>
+        <v>2600</v>
       </c>
       <c r="H92" s="2">
-        <v>45989.83333333334</v>
+        <v>45989.53125</v>
       </c>
       <c r="I92" s="2">
-        <v>45989.83333333334</v>
+        <v>45989.53125</v>
       </c>
       <c r="J92" s="2">
-        <v>45991.16837712096</v>
+        <v>45990.68444318017</v>
       </c>
       <c r="K92" t="s">
         <v>102</v>
@@ -5539,7 +5536,7 @@
         <v>102</v>
       </c>
       <c r="N92">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O92">
         <v>0</v>
@@ -5551,7 +5548,7 @@
         <v>102</v>
       </c>
       <c r="R92">
-        <v>32.04105090305556</v>
+        <v>27.67663632416667</v>
       </c>
     </row>
     <row r="93" spans="1:18">
@@ -5559,28 +5556,28 @@
         <v>63</v>
       </c>
       <c r="B93" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C93" t="s">
         <v>100</v>
       </c>
       <c r="D93">
-        <v>6.769936468817598</v>
+        <v>13.03904891423422</v>
       </c>
       <c r="E93">
         <v>62.21893992770459</v>
       </c>
       <c r="F93">
-        <v>440.0458704731439</v>
+        <v>847.5381794252241</v>
       </c>
       <c r="G93">
-        <v>3150</v>
+        <v>2600</v>
       </c>
       <c r="H93" s="2">
-        <v>45985.04166666666</v>
+        <v>45984.9375</v>
       </c>
       <c r="J93" s="2">
-        <v>45985.68485846398</v>
+        <v>45986.11621037142</v>
       </c>
       <c r="K93" t="s">
         <v>102</v>
@@ -5592,7 +5589,7 @@
         <v>102</v>
       </c>
       <c r="N93">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O93">
         <v>0</v>
@@ -5604,7 +5601,7 @@
         <v>102</v>
       </c>
       <c r="R93">
-        <v>15.43660313555556</v>
+        <v>28.28904891416667</v>
       </c>
     </row>
     <row r="94" spans="1:18">
@@ -5612,7 +5609,7 @@
         <v>64</v>
       </c>
       <c r="B94" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C94" t="s">
         <v>100</v>
@@ -5627,16 +5624,16 @@
         <v>0.3</v>
       </c>
       <c r="G94">
-        <v>2250</v>
+        <v>1500</v>
       </c>
       <c r="H94" s="2">
-        <v>45989.83333333334</v>
+        <v>45989.53125</v>
       </c>
       <c r="I94" s="2">
-        <v>45989.83333333334</v>
+        <v>45989.53125</v>
       </c>
       <c r="J94" s="2">
-        <v>45991.16837712096</v>
+        <v>45990.68444318017</v>
       </c>
       <c r="K94" t="s">
         <v>102</v>
@@ -5645,7 +5642,7 @@
         <v>102</v>
       </c>
       <c r="N94">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -5657,7 +5654,7 @@
         <v>102</v>
       </c>
       <c r="R94">
-        <v>32.04105090305556</v>
+        <v>27.67663632416667</v>
       </c>
     </row>
     <row r="95" spans="1:18">
@@ -5665,28 +5662,28 @@
         <v>64</v>
       </c>
       <c r="B95" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C95" t="s">
         <v>100</v>
       </c>
       <c r="D95">
-        <v>6.769936468817598</v>
+        <v>13.03904891423422</v>
       </c>
       <c r="E95">
         <v>62.21893992770459</v>
       </c>
       <c r="F95">
-        <v>440.0458704731439</v>
+        <v>847.5381794252241</v>
       </c>
       <c r="G95">
-        <v>2250</v>
+        <v>1500</v>
       </c>
       <c r="H95" s="2">
-        <v>45985.04166666666</v>
+        <v>45984.9375</v>
       </c>
       <c r="J95" s="2">
-        <v>45985.68485846398</v>
+        <v>45986.11621037142</v>
       </c>
       <c r="K95" t="s">
         <v>102</v>
@@ -5698,7 +5695,7 @@
         <v>102</v>
       </c>
       <c r="N95">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O95">
         <v>0</v>
@@ -5710,7 +5707,7 @@
         <v>102</v>
       </c>
       <c r="R95">
-        <v>15.43660313555556</v>
+        <v>28.28904891416667</v>
       </c>
     </row>
     <row r="96" spans="1:18">
@@ -5718,31 +5715,31 @@
         <v>65</v>
       </c>
       <c r="B96" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C96" t="s">
         <v>101</v>
       </c>
       <c r="D96">
-        <v>3.415313225058004</v>
+        <v>3.488151658767772</v>
       </c>
       <c r="E96">
         <v>16</v>
       </c>
       <c r="F96">
-        <v>221.9953596287703</v>
+        <v>226.7298578199052</v>
       </c>
       <c r="G96">
         <v>2100</v>
       </c>
       <c r="H96" s="2">
-        <v>45989.71875</v>
+        <v>45989.41666666666</v>
       </c>
       <c r="I96" s="2">
-        <v>45989.80208333334</v>
+        <v>45989.5</v>
       </c>
       <c r="J96" s="2">
-        <v>45990.15272138437</v>
+        <v>45989.85367298579</v>
       </c>
       <c r="K96" t="s">
         <v>102</v>
@@ -5757,13 +5754,13 @@
         <v>0</v>
       </c>
       <c r="P96">
-        <v>3.415313225058004</v>
+        <v>3.488151658767772</v>
       </c>
       <c r="Q96">
         <v>2</v>
       </c>
       <c r="R96">
-        <v>10.415313225</v>
+        <v>10.48815165888889</v>
       </c>
     </row>
     <row r="97" spans="1:18">
@@ -5771,31 +5768,31 @@
         <v>66</v>
       </c>
       <c r="B97" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C97" t="s">
         <v>101</v>
       </c>
       <c r="D97">
-        <v>3.415313225058004</v>
+        <v>3.488151658767772</v>
       </c>
       <c r="E97">
         <v>16</v>
       </c>
       <c r="F97">
-        <v>221.9953596287703</v>
+        <v>226.7298578199052</v>
       </c>
       <c r="G97">
         <v>2100</v>
       </c>
       <c r="H97" s="2">
-        <v>45989.71875</v>
+        <v>45989.41666666666</v>
       </c>
       <c r="I97" s="2">
-        <v>45989.80208333334</v>
+        <v>45989.5</v>
       </c>
       <c r="J97" s="2">
-        <v>45990.15272138437</v>
+        <v>45989.85367298579</v>
       </c>
       <c r="K97" t="s">
         <v>102</v>
@@ -5810,13 +5807,13 @@
         <v>0</v>
       </c>
       <c r="P97">
-        <v>3.415313225058004</v>
+        <v>3.488151658767772</v>
       </c>
       <c r="Q97">
         <v>2</v>
       </c>
       <c r="R97">
-        <v>10.415313225</v>
+        <v>10.48815165888889</v>
       </c>
     </row>
     <row r="98" spans="1:18">
@@ -5824,31 +5821,31 @@
         <v>67</v>
       </c>
       <c r="B98" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C98" t="s">
         <v>101</v>
       </c>
       <c r="D98">
-        <v>3.415313225058004</v>
+        <v>3.488151658767772</v>
       </c>
       <c r="E98">
         <v>16</v>
       </c>
       <c r="F98">
-        <v>221.9953596287703</v>
+        <v>226.7298578199052</v>
       </c>
       <c r="G98">
         <v>2250</v>
       </c>
       <c r="H98" s="2">
-        <v>45989.71875</v>
+        <v>45989.41666666666</v>
       </c>
       <c r="I98" s="2">
-        <v>45989.80208333334</v>
+        <v>45989.5</v>
       </c>
       <c r="J98" s="2">
-        <v>45990.15272138437</v>
+        <v>45989.85367298579</v>
       </c>
       <c r="K98" t="s">
         <v>102</v>
@@ -5863,13 +5860,13 @@
         <v>0</v>
       </c>
       <c r="P98">
-        <v>3.415313225058004</v>
+        <v>3.488151658767772</v>
       </c>
       <c r="Q98">
         <v>2</v>
       </c>
       <c r="R98">
-        <v>10.415313225</v>
+        <v>10.48815165888889</v>
       </c>
     </row>
     <row r="99" spans="1:18">
@@ -5877,31 +5874,31 @@
         <v>68</v>
       </c>
       <c r="B99" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C99" t="s">
         <v>101</v>
       </c>
       <c r="D99">
-        <v>3.415313225058004</v>
+        <v>3.488151658767772</v>
       </c>
       <c r="E99">
         <v>16</v>
       </c>
       <c r="F99">
-        <v>221.9953596287703</v>
+        <v>226.7298578199052</v>
       </c>
       <c r="G99">
         <v>2100</v>
       </c>
       <c r="H99" s="2">
-        <v>45989.71875</v>
+        <v>45989.41666666666</v>
       </c>
       <c r="I99" s="2">
-        <v>45989.80208333334</v>
+        <v>45989.5</v>
       </c>
       <c r="J99" s="2">
-        <v>45990.15272138437</v>
+        <v>45989.85367298579</v>
       </c>
       <c r="K99" t="s">
         <v>102</v>
@@ -5916,45 +5913,45 @@
         <v>0</v>
       </c>
       <c r="P99">
-        <v>3.415313225058004</v>
+        <v>3.488151658767772</v>
       </c>
       <c r="Q99">
         <v>2</v>
       </c>
       <c r="R99">
-        <v>10.415313225</v>
+        <v>10.48815165888889</v>
       </c>
     </row>
     <row r="100" spans="1:18">
       <c r="A100" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B100" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C100" t="s">
         <v>101</v>
       </c>
       <c r="D100">
-        <v>3.415313225058004</v>
+        <v>3.488151658767772</v>
       </c>
       <c r="E100">
         <v>16</v>
       </c>
       <c r="F100">
-        <v>221.9953596287703</v>
+        <v>226.7298578199052</v>
       </c>
       <c r="G100">
-        <v>2100</v>
+        <v>2500</v>
       </c>
       <c r="H100" s="2">
-        <v>45989.71875</v>
+        <v>45989.41666666666</v>
       </c>
       <c r="I100" s="2">
-        <v>45989.80208333334</v>
+        <v>45989.5</v>
       </c>
       <c r="J100" s="2">
-        <v>45990.15272138437</v>
+        <v>45989.85367298579</v>
       </c>
       <c r="K100" t="s">
         <v>102</v>
@@ -5969,45 +5966,45 @@
         <v>0</v>
       </c>
       <c r="P100">
-        <v>3.415313225058004</v>
+        <v>3.488151658767772</v>
       </c>
       <c r="Q100">
         <v>2</v>
       </c>
       <c r="R100">
-        <v>10.415313225</v>
+        <v>10.48815165888889</v>
       </c>
     </row>
     <row r="101" spans="1:18">
       <c r="A101" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B101" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C101" t="s">
         <v>101</v>
       </c>
       <c r="D101">
-        <v>3.415313225058004</v>
+        <v>3.488151658767772</v>
       </c>
       <c r="E101">
         <v>16</v>
       </c>
       <c r="F101">
-        <v>221.9953596287703</v>
+        <v>226.7298578199052</v>
       </c>
       <c r="G101">
-        <v>2200</v>
+        <v>2250</v>
       </c>
       <c r="H101" s="2">
-        <v>45989.71875</v>
+        <v>45989.41666666666</v>
       </c>
       <c r="I101" s="2">
-        <v>45989.80208333334</v>
+        <v>45989.5</v>
       </c>
       <c r="J101" s="2">
-        <v>45990.15272138437</v>
+        <v>45989.85367298579</v>
       </c>
       <c r="K101" t="s">
         <v>102</v>
@@ -6022,45 +6019,45 @@
         <v>0</v>
       </c>
       <c r="P101">
-        <v>3.415313225058004</v>
+        <v>3.488151658767772</v>
       </c>
       <c r="Q101">
         <v>2</v>
       </c>
       <c r="R101">
-        <v>10.415313225</v>
+        <v>10.48815165888889</v>
       </c>
     </row>
     <row r="102" spans="1:18">
       <c r="A102" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B102" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C102" t="s">
         <v>101</v>
       </c>
       <c r="D102">
-        <v>2.909090909090909</v>
+        <v>2.885771543086173</v>
       </c>
       <c r="E102">
         <v>16</v>
       </c>
       <c r="F102">
-        <v>189.0909090909091</v>
+        <v>187.5751503006012</v>
       </c>
       <c r="G102">
-        <v>2500</v>
+        <v>2100</v>
       </c>
       <c r="H102" s="2">
-        <v>45992.20833333334</v>
+        <v>45992.29166666666</v>
       </c>
       <c r="I102" s="2">
-        <v>45992.28125</v>
+        <v>45992.36521464647</v>
       </c>
       <c r="J102" s="2">
-        <v>45992.57607323233</v>
+        <v>45992.65906623854</v>
       </c>
       <c r="K102" t="s">
         <v>102</v>
@@ -6075,45 +6072,45 @@
         <v>0</v>
       </c>
       <c r="P102">
-        <v>2.909090909090909</v>
+        <v>2.885771543086173</v>
       </c>
       <c r="Q102">
         <v>2</v>
       </c>
       <c r="R102">
-        <v>8.825757575833334</v>
+        <v>8.817589724999999</v>
       </c>
     </row>
     <row r="103" spans="1:18">
       <c r="A103" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B103" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C103" t="s">
         <v>101</v>
       </c>
       <c r="D103">
-        <v>2.909090909090909</v>
+        <v>2.885771543086173</v>
       </c>
       <c r="E103">
         <v>16</v>
       </c>
       <c r="F103">
-        <v>189.0909090909091</v>
+        <v>187.5751503006012</v>
       </c>
       <c r="G103">
-        <v>2250</v>
+        <v>2200</v>
       </c>
       <c r="H103" s="2">
-        <v>45992.20833333334</v>
+        <v>45992.29166666666</v>
       </c>
       <c r="I103" s="2">
-        <v>45992.28125</v>
+        <v>45992.36521464647</v>
       </c>
       <c r="J103" s="2">
-        <v>45992.57607323233</v>
+        <v>45992.65906623854</v>
       </c>
       <c r="K103" t="s">
         <v>102</v>
@@ -6128,45 +6125,45 @@
         <v>0</v>
       </c>
       <c r="P103">
-        <v>2.909090909090909</v>
+        <v>2.885771543086173</v>
       </c>
       <c r="Q103">
         <v>2</v>
       </c>
       <c r="R103">
-        <v>8.825757575833334</v>
+        <v>8.817589724999999</v>
       </c>
     </row>
     <row r="104" spans="1:18">
       <c r="A104" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="B104" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C104" t="s">
         <v>101</v>
       </c>
       <c r="D104">
-        <v>2.909090909090909</v>
+        <v>2.885771543086173</v>
       </c>
       <c r="E104">
         <v>16</v>
       </c>
       <c r="F104">
-        <v>189.0909090909091</v>
+        <v>187.5751503006012</v>
       </c>
       <c r="G104">
-        <v>2250</v>
+        <v>2750</v>
       </c>
       <c r="H104" s="2">
-        <v>45992.20833333334</v>
+        <v>45992.29166666666</v>
       </c>
       <c r="I104" s="2">
-        <v>45992.28125</v>
+        <v>45992.36521464647</v>
       </c>
       <c r="J104" s="2">
-        <v>45992.57607323233</v>
+        <v>45992.65906623854</v>
       </c>
       <c r="K104" t="s">
         <v>102</v>
@@ -6181,45 +6178,45 @@
         <v>0</v>
       </c>
       <c r="P104">
-        <v>2.909090909090909</v>
+        <v>2.885771543086173</v>
       </c>
       <c r="Q104">
         <v>2</v>
       </c>
       <c r="R104">
-        <v>8.825757575833334</v>
+        <v>8.817589724999999</v>
       </c>
     </row>
     <row r="105" spans="1:18">
       <c r="A105" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B105" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C105" t="s">
         <v>101</v>
       </c>
       <c r="D105">
-        <v>2.909090909090909</v>
+        <v>2.885771543086173</v>
       </c>
       <c r="E105">
         <v>16</v>
       </c>
       <c r="F105">
-        <v>189.0909090909091</v>
+        <v>187.5751503006012</v>
       </c>
       <c r="G105">
-        <v>2750</v>
+        <v>2500</v>
       </c>
       <c r="H105" s="2">
-        <v>45992.20833333334</v>
+        <v>45992.29166666666</v>
       </c>
       <c r="I105" s="2">
-        <v>45992.28125</v>
+        <v>45992.36521464647</v>
       </c>
       <c r="J105" s="2">
-        <v>45992.57607323233</v>
+        <v>45992.65906623854</v>
       </c>
       <c r="K105" t="s">
         <v>102</v>
@@ -6234,45 +6231,45 @@
         <v>0</v>
       </c>
       <c r="P105">
-        <v>2.909090909090909</v>
+        <v>2.885771543086173</v>
       </c>
       <c r="Q105">
         <v>2</v>
       </c>
       <c r="R105">
-        <v>8.825757575833334</v>
+        <v>8.817589724999999</v>
       </c>
     </row>
     <row r="106" spans="1:18">
       <c r="A106" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B106" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C106" t="s">
         <v>101</v>
       </c>
       <c r="D106">
-        <v>2.909090909090909</v>
+        <v>2.885771543086173</v>
       </c>
       <c r="E106">
         <v>16</v>
       </c>
       <c r="F106">
-        <v>189.0909090909091</v>
+        <v>187.5751503006012</v>
       </c>
       <c r="G106">
         <v>2500</v>
       </c>
       <c r="H106" s="2">
-        <v>45992.20833333334</v>
+        <v>45992.29166666666</v>
       </c>
       <c r="I106" s="2">
-        <v>45992.28125</v>
+        <v>45992.36521464647</v>
       </c>
       <c r="J106" s="2">
-        <v>45992.57607323233</v>
+        <v>45992.65906623854</v>
       </c>
       <c r="K106" t="s">
         <v>102</v>
@@ -6287,45 +6284,45 @@
         <v>0</v>
       </c>
       <c r="P106">
-        <v>2.909090909090909</v>
+        <v>2.885771543086173</v>
       </c>
       <c r="Q106">
         <v>2</v>
       </c>
       <c r="R106">
-        <v>8.825757575833334</v>
+        <v>8.817589724999999</v>
       </c>
     </row>
     <row r="107" spans="1:18">
       <c r="A107" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B107" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="C107" t="s">
         <v>101</v>
       </c>
       <c r="D107">
-        <v>2.840236686390533</v>
+        <v>1.756862745098039</v>
       </c>
       <c r="E107">
         <v>16</v>
       </c>
       <c r="F107">
-        <v>184.6153846153846</v>
+        <v>114.1960784313725</v>
       </c>
       <c r="G107">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="H107" s="2">
-        <v>45993.16666666666</v>
+        <v>45994.28125</v>
       </c>
       <c r="I107" s="2">
-        <v>45993.22916666666</v>
+        <v>45994.3125</v>
       </c>
       <c r="J107" s="2">
-        <v>45993.49878574664</v>
+        <v>45994.46753405464</v>
       </c>
       <c r="K107" t="s">
         <v>102</v>
@@ -6334,51 +6331,51 @@
         <v>102</v>
       </c>
       <c r="N107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O107">
         <v>0</v>
       </c>
       <c r="P107">
-        <v>2.840236686390533</v>
+        <v>1.756862745098039</v>
       </c>
       <c r="Q107">
         <v>2</v>
       </c>
       <c r="R107">
-        <v>7.970857919444445</v>
+        <v>4.470817311388889</v>
       </c>
     </row>
     <row r="108" spans="1:18">
       <c r="A108" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B108" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="C108" t="s">
         <v>101</v>
       </c>
       <c r="D108">
-        <v>2.840236686390533</v>
+        <v>1.756862745098039</v>
       </c>
       <c r="E108">
         <v>16</v>
       </c>
       <c r="F108">
-        <v>184.6153846153846</v>
+        <v>114.1960784313725</v>
       </c>
       <c r="G108">
-        <v>2900</v>
+        <v>3150</v>
       </c>
       <c r="H108" s="2">
-        <v>45993.16666666666</v>
+        <v>45994.28125</v>
       </c>
       <c r="I108" s="2">
-        <v>45993.22916666666</v>
+        <v>45994.3125</v>
       </c>
       <c r="J108" s="2">
-        <v>45993.49878574664</v>
+        <v>45994.46753405464</v>
       </c>
       <c r="K108" t="s">
         <v>102</v>
@@ -6387,24 +6384,24 @@
         <v>102</v>
       </c>
       <c r="N108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O108">
         <v>0</v>
       </c>
       <c r="P108">
-        <v>2.840236686390533</v>
+        <v>1.756862745098039</v>
       </c>
       <c r="Q108">
         <v>2</v>
       </c>
       <c r="R108">
-        <v>7.970857919444445</v>
+        <v>4.470817311388889</v>
       </c>
     </row>
     <row r="109" spans="1:18">
       <c r="A109" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B109" t="s">
         <v>97</v>
@@ -6413,25 +6410,25 @@
         <v>101</v>
       </c>
       <c r="D109">
-        <v>2.840236686390533</v>
+        <v>2.400393507132316</v>
       </c>
       <c r="E109">
         <v>16</v>
       </c>
       <c r="F109">
-        <v>184.6153846153846</v>
+        <v>156.0255779636006</v>
       </c>
       <c r="G109">
-        <v>2750</v>
+        <v>2100</v>
       </c>
       <c r="H109" s="2">
-        <v>45993.16666666666</v>
+        <v>45994.27083333334</v>
       </c>
       <c r="I109" s="2">
-        <v>45993.22916666666</v>
+        <v>45994.3125</v>
       </c>
       <c r="J109" s="2">
-        <v>45993.49878574664</v>
+        <v>45994.54295894751</v>
       </c>
       <c r="K109" t="s">
         <v>102</v>
@@ -6440,24 +6437,24 @@
         <v>102</v>
       </c>
       <c r="N109">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O109">
         <v>0</v>
       </c>
       <c r="P109">
-        <v>2.840236686390533</v>
+        <v>2.400393507132316</v>
       </c>
       <c r="Q109">
         <v>2</v>
       </c>
       <c r="R109">
-        <v>7.970857919444445</v>
+        <v>6.531014740277778</v>
       </c>
     </row>
     <row r="110" spans="1:18">
       <c r="A110" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B110" t="s">
         <v>97</v>
@@ -6466,25 +6463,25 @@
         <v>101</v>
       </c>
       <c r="D110">
-        <v>2.840236686390533</v>
+        <v>2.400393507132316</v>
       </c>
       <c r="E110">
         <v>16</v>
       </c>
       <c r="F110">
-        <v>184.6153846153846</v>
+        <v>156.0255779636006</v>
       </c>
       <c r="G110">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="H110" s="2">
-        <v>45993.16666666666</v>
+        <v>45994.27083333334</v>
       </c>
       <c r="I110" s="2">
-        <v>45993.22916666666</v>
+        <v>45994.3125</v>
       </c>
       <c r="J110" s="2">
-        <v>45993.49878574664</v>
+        <v>45994.54295894751</v>
       </c>
       <c r="K110" t="s">
         <v>102</v>
@@ -6493,51 +6490,51 @@
         <v>102</v>
       </c>
       <c r="N110">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O110">
         <v>0</v>
       </c>
       <c r="P110">
-        <v>2.840236686390533</v>
+        <v>2.400393507132316</v>
       </c>
       <c r="Q110">
         <v>2</v>
       </c>
       <c r="R110">
-        <v>7.970857919444445</v>
+        <v>6.531014740277778</v>
       </c>
     </row>
     <row r="111" spans="1:18">
       <c r="A111" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B111" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C111" t="s">
         <v>101</v>
       </c>
       <c r="D111">
-        <v>1.921787709497207</v>
+        <v>2.400393507132316</v>
       </c>
       <c r="E111">
         <v>16</v>
       </c>
       <c r="F111">
-        <v>124.9162011173184</v>
+        <v>156.0255779636006</v>
       </c>
       <c r="G111">
-        <v>2600</v>
+        <v>3150</v>
       </c>
       <c r="H111" s="2">
-        <v>45994.44791666666</v>
+        <v>45994.27083333334</v>
       </c>
       <c r="I111" s="2">
-        <v>45994.48958333334</v>
+        <v>45994.3125</v>
       </c>
       <c r="J111" s="2">
-        <v>45994.70326893234</v>
+        <v>45994.54295894751</v>
       </c>
       <c r="K111" t="s">
         <v>102</v>
@@ -6552,45 +6549,45 @@
         <v>0</v>
       </c>
       <c r="P111">
-        <v>1.921787709497207</v>
+        <v>2.400393507132316</v>
       </c>
       <c r="Q111">
         <v>2</v>
       </c>
       <c r="R111">
-        <v>6.128454376111111</v>
+        <v>6.531014740277778</v>
       </c>
     </row>
     <row r="112" spans="1:18">
       <c r="A112" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B112" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C112" t="s">
         <v>101</v>
       </c>
       <c r="D112">
-        <v>1.921787709497207</v>
+        <v>2.892906815020862</v>
       </c>
       <c r="E112">
         <v>16</v>
       </c>
       <c r="F112">
-        <v>124.9162011173184</v>
+        <v>188.0389429763561</v>
       </c>
       <c r="G112">
-        <v>3150</v>
+        <v>2900</v>
       </c>
       <c r="H112" s="2">
-        <v>45994.44791666666</v>
+        <v>45994.25</v>
       </c>
       <c r="I112" s="2">
-        <v>45994.48958333334</v>
+        <v>45994.3125</v>
       </c>
       <c r="J112" s="2">
-        <v>45994.70326893234</v>
+        <v>45994.57192667285</v>
       </c>
       <c r="K112" t="s">
         <v>102</v>
@@ -6599,51 +6596,51 @@
         <v>102</v>
       </c>
       <c r="N112">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O112">
         <v>0</v>
       </c>
       <c r="P112">
-        <v>1.921787709497207</v>
+        <v>2.892906815020862</v>
       </c>
       <c r="Q112">
         <v>2</v>
       </c>
       <c r="R112">
-        <v>6.128454376111111</v>
+        <v>7.726240148333333</v>
       </c>
     </row>
     <row r="113" spans="1:18">
       <c r="A113" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B113" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C113" t="s">
         <v>101</v>
       </c>
       <c r="D113">
-        <v>1.921787709497207</v>
+        <v>2.892906815020862</v>
       </c>
       <c r="E113">
         <v>16</v>
       </c>
       <c r="F113">
-        <v>124.9162011173184</v>
+        <v>188.0389429763561</v>
       </c>
       <c r="G113">
-        <v>250</v>
+        <v>2750</v>
       </c>
       <c r="H113" s="2">
-        <v>45994.44791666666</v>
+        <v>45994.25</v>
       </c>
       <c r="I113" s="2">
-        <v>45994.48958333334</v>
+        <v>45994.3125</v>
       </c>
       <c r="J113" s="2">
-        <v>45994.70326893234</v>
+        <v>45994.57192667285</v>
       </c>
       <c r="K113" t="s">
         <v>102</v>
@@ -6652,24 +6649,24 @@
         <v>102</v>
       </c>
       <c r="N113">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O113">
         <v>0</v>
       </c>
       <c r="P113">
-        <v>1.921787709497207</v>
+        <v>2.892906815020862</v>
       </c>
       <c r="Q113">
         <v>2</v>
       </c>
       <c r="R113">
-        <v>6.128454376111111</v>
+        <v>7.726240148333333</v>
       </c>
     </row>
     <row r="114" spans="1:18">
       <c r="A114" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B114" t="s">
         <v>88</v>
@@ -6678,25 +6675,25 @@
         <v>101</v>
       </c>
       <c r="D114">
-        <v>2.448569994982438</v>
+        <v>2.892906815020862</v>
       </c>
       <c r="E114">
         <v>16</v>
       </c>
       <c r="F114">
-        <v>159.1570496738585</v>
+        <v>188.0389429763561</v>
       </c>
       <c r="G114">
-        <v>2900</v>
+        <v>2600</v>
       </c>
       <c r="H114" s="2">
-        <v>45994.44791666666</v>
+        <v>45994.25</v>
       </c>
       <c r="I114" s="2">
-        <v>45994.48958333334</v>
+        <v>45994.3125</v>
       </c>
       <c r="J114" s="2">
-        <v>45994.71132930535</v>
+        <v>45994.57192667285</v>
       </c>
       <c r="K114" t="s">
         <v>102</v>
@@ -6705,24 +6702,24 @@
         <v>102</v>
       </c>
       <c r="N114">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O114">
         <v>0</v>
       </c>
       <c r="P114">
-        <v>2.448569994982438</v>
+        <v>2.892906815020862</v>
       </c>
       <c r="Q114">
         <v>2</v>
       </c>
       <c r="R114">
-        <v>6.321903328333334</v>
+        <v>7.726240148333333</v>
       </c>
     </row>
     <row r="115" spans="1:18">
       <c r="A115" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B115" t="s">
         <v>88</v>
@@ -6731,25 +6728,25 @@
         <v>101</v>
       </c>
       <c r="D115">
-        <v>2.448569994982438</v>
+        <v>2.892906815020862</v>
       </c>
       <c r="E115">
         <v>16</v>
       </c>
       <c r="F115">
-        <v>159.1570496738585</v>
+        <v>188.0389429763561</v>
       </c>
       <c r="G115">
-        <v>3150</v>
+        <v>2900</v>
       </c>
       <c r="H115" s="2">
-        <v>45994.44791666666</v>
+        <v>45994.25</v>
       </c>
       <c r="I115" s="2">
-        <v>45994.48958333334</v>
+        <v>45994.3125</v>
       </c>
       <c r="J115" s="2">
-        <v>45994.71132930535</v>
+        <v>45994.57192667285</v>
       </c>
       <c r="K115" t="s">
         <v>102</v>
@@ -6758,72 +6755,19 @@
         <v>102</v>
       </c>
       <c r="N115">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O115">
         <v>0</v>
       </c>
       <c r="P115">
-        <v>2.448569994982438</v>
+        <v>2.892906815020862</v>
       </c>
       <c r="Q115">
         <v>2</v>
       </c>
       <c r="R115">
-        <v>6.321903328333334</v>
-      </c>
-    </row>
-    <row r="116" spans="1:18">
-      <c r="A116" t="s">
-        <v>80</v>
-      </c>
-      <c r="B116" t="s">
-        <v>88</v>
-      </c>
-      <c r="C116" t="s">
-        <v>101</v>
-      </c>
-      <c r="D116">
-        <v>2.448569994982438</v>
-      </c>
-      <c r="E116">
-        <v>16</v>
-      </c>
-      <c r="F116">
-        <v>159.1570496738585</v>
-      </c>
-      <c r="G116">
-        <v>2100</v>
-      </c>
-      <c r="H116" s="2">
-        <v>45994.44791666666</v>
-      </c>
-      <c r="I116" s="2">
-        <v>45994.48958333334</v>
-      </c>
-      <c r="J116" s="2">
-        <v>45994.71132930535</v>
-      </c>
-      <c r="K116" t="s">
-        <v>102</v>
-      </c>
-      <c r="M116" t="s">
-        <v>102</v>
-      </c>
-      <c r="N116">
-        <v>1.5</v>
-      </c>
-      <c r="O116">
-        <v>0</v>
-      </c>
-      <c r="P116">
-        <v>2.448569994982438</v>
-      </c>
-      <c r="Q116">
-        <v>2</v>
-      </c>
-      <c r="R116">
-        <v>6.321903328333334</v>
+        <v>7.726240148333333</v>
       </c>
     </row>
   </sheetData>
